--- a/backend/exports/All_Extracted_Leads.xlsx
+++ b/backend/exports/All_Extracted_Leads.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Leads" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$O$184</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$Q$191</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,24 +419,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O184"/>
+  <dimension ref="A1:Q191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="50" customWidth="1" min="10" max="10"/>
-    <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
     <col width="50" customWidth="1" min="12" max="12"/>
     <col width="50" customWidth="1" min="13" max="13"/>
     <col width="50" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="50" customWidth="1" min="15" max="15"/>
+    <col width="50" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -452,65 +454,75 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>GST Confidence</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>GST Sources</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Turn Over</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Region</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Industry Type</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Contact Person</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Designation</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Mobile Number</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Alternate Mobile Number</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Email ID</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>LinkedIN Id</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Website URL</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Followup</t>
         </is>
@@ -522,32 +534,32 @@
           <t>Aira Euromatic (Ball Valve|PRV|Gate Valve|Butterfly Valve|Solenoid Valve Manufacturer, Supplier &amp; Dealer)</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>099622 73778</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>chennai@airaindia.com</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>https://www.airaindia.com/valves-in-chennai/?utm_source=gmb&amp;utm_medium=referral</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -559,37 +571,37 @@
           <t>Tubes &amp; Valves Manufacturing company</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Ward 60</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>080120 11666</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>sales@tubesandvalves.com</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>http://www.tubesandvalves.com/</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -601,37 +613,37 @@
           <t>Fluid Valve Company</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Zone 5 Royapuram</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>080 4898 6736</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>fluidvalveco@gmail.com</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>http://www.fluidvalveco.com/</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -643,37 +655,37 @@
           <t>Amco Industrial Valves</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Zone 1 Tiruvottiyur</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>098848 11802</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>contact@amcovalves.com</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>https://amcovalves.com/</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -685,32 +697,32 @@
           <t>Unique Industrial Valves, Valves Manufacturers, Unique Control Systems.</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>063695 99499</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>controlsystems28@gmail.com</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>http://www.uniquecontrolsystems.com/</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -722,37 +734,37 @@
           <t>Lehry Instrumentation &amp; Valves Pvt Ltd</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Zone 5 Royapuram</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>044 2522 5185</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>info@lehryvalves.com</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>https://lehryvalves.com/</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -764,37 +776,37 @@
           <t>Xtreme Valves</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Zone 7 Ambattur</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>098840 81734</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>sales@xvalves.com</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>http://www.xvalves.com/</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -806,37 +818,37 @@
           <t>HITEC VALVES</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Zone 7 Ambattur</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>094448 62329</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>hitecvalves@vsnl.net</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>http://www.hitecvalves.com/</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -848,37 +860,37 @@
           <t>HP Valves &amp; Fittings India (P) LTD. - Unit- 2</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Zone 7 Ambattur</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>044 2625 2537</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>sales@hpvalvesindia.com</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>https://hpvalvesindia.com/</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -890,32 +902,32 @@
           <t>Adnan Allied</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Zone 5 Royapuram</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>navkarinte@yahoo.co.in</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>http://www.adnanallied.in/</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -927,42 +939,42 @@
           <t>DYNAMIC CONTROLS &amp; SERVICES</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>Mr. G Natarajan</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>098408 98063</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>sales@dynamiccontrols.in</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>http://www.dynamiccontrols.in/</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -974,32 +986,32 @@
           <t>Integrated Valves &amp; Fittings Pvt Ltd</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>094443 24323</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>integratedvalves2014@gmail.com</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>http://www.integratedvalves.com/</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -1011,32 +1023,32 @@
           <t>Shekhi Traders, Dealers in Brass Valves</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Zone 5 Royapuram</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>098410 54899</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>https://sites.google.com/view/shekhi-traders/home</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -1048,32 +1060,32 @@
           <t>Power Flow Hydraulics/Hydraulic Valves/Hydraulic Pumps/Hydraulic Motors/Electrical Motors/Dealers/chennai</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Duraisamypuram S</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>098844 01494</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>powerflowhydraulics@gmail.com</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>http://powerflowhydraulics.in/</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -1085,32 +1097,32 @@
           <t>Floport Valves Private Limited</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Ambattur</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>094440 55503</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>mkumarassociates@gmail.com</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>http://floportvalves.in/</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -1122,32 +1134,32 @@
           <t>SMC Pneumatic Store - Chennai</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Zone 7 Ambattur</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>072009 52222</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>https://smc-pneumatic-store-chennai.localo.site/?utm_source=google_profile&amp;utm_campaign=localo&amp;utm_medium=mainlink</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -1159,32 +1171,32 @@
           <t>S. Abbas &amp; Co. - dealer for water meter , valves ,pipes , honeywell actuators, ibr fittings</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Ward 60</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>044 2522 8525</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>https://alivalves.in/</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -1196,32 +1208,32 @@
           <t>Blendsteel Engineering Private Limited</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Ward 197</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>sales@blendsteel.com</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>https://www.blendsteel.com/</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -1238,32 +1250,32 @@
           <t>33BVBPS8271G2ZD</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>098848 80421</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>aehvacsales01@gmail.com</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>https://akshayaenterprises.net/</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -1275,32 +1287,32 @@
           <t>Sri sai valve automation</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Pozhichalur</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>valveservice@srisaivalve.in</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>http://www.srisaivalve.in/</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -1312,27 +1324,27 @@
           <t>ValvTechnologies Private limited</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>info@valv.com</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>http://www.valv.com/</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -1344,42 +1356,42 @@
           <t>SUPREME CONTROLING VALVE PRIVATE LIMITED</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>Ward 139</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>098402 16533</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>www.supremefluidcontrol.com</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/supremefluid-control-429959166/</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>http://supremefluidcontrol.com/</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -1391,37 +1403,37 @@
           <t>Jameel Trading Company</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>Zone 5 Royapuram</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>044 4216 0195</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>jtc@jameeltrading.com</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>https://www.jameeltrading.com/</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -1433,37 +1445,37 @@
           <t>Ezzi Hardware - Valves, Pipes &amp; Fittings</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Zone 5 Royapuram</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>044 2521 0167</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>sales@ezzihardware.com</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>http://ezzihardware.com/</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -1475,32 +1487,32 @@
           <t>FLOIN VALVES AND INSTRUMENTS</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>063749 89478</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>sales@floinvalves.com</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>http://floinvalves.com/</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -1512,37 +1524,37 @@
           <t>Asian Valve Components</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>Chennai district</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>063834 72692</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>purushothaman@asianvalvecomponents.co.in</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>https://www.asianvalvecomponents.co.in/</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -1554,32 +1566,32 @@
           <t>Severn Glocon Valves Private Limited</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>Sriperumbudur</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>044 4710 4200</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>marketing@severnvalve.com</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>http://www.severnglocon.com/</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -1596,37 +1608,37 @@
           <t>33ABNCS6715M1ZT</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>Zone 11 Valasaravakkam</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>073587 55442</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>info@smiv.in</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>https://www.smiv.in/</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -1638,32 +1650,32 @@
           <t>RANEE ENTERPRISES</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>Zone 5 Royapuram</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>073583 76749</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>director@greenwaysgroup.in</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -1675,37 +1687,37 @@
           <t>Uniflow</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>Zone 10 Kodambakkam</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>044 2625 8836</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>vaithy@uniflowvalves.com</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>http://www.uniflowvalves.com/</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -1717,32 +1729,32 @@
           <t>Ponnar Valves India Private Limited</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>074187 21569</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>sales@ponnarvalves.com</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>https://www.ponnarvalves.com/</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -1754,37 +1766,37 @@
           <t>Bharat Industrial Valve | Valves Flanges and Fittings</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>Tondiarpet</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>080562 62588</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>bharatindustrialvalve@gmail.com</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>https://www.bharatindustrialvalve.com/</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -1801,37 +1813,37 @@
           <t>33AAAPF0374J1Z5</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>Zone 5 Royapuram</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>080 4898 9631</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>ntcsaif@hotmail.com</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>http://nobletradecentre.in/</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -1843,32 +1855,32 @@
           <t>Redbridge valves</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>Zone 5 Royapuram</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>sales@redbridgevalves.com</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>http://redbridgevalves.com/</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -1880,32 +1892,32 @@
           <t>AM-PRODUCTS (VAL-LUBRIC)</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>063797 48910</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>info@val-lubric.com</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>http://www.val-lubric.com/</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -1917,32 +1929,32 @@
           <t>Emaar Valves and Controls</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>Kundrathur</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>098840 09911</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>sales@emaarvalves.in</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>http://emaarvalves.in/</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -1954,37 +1966,37 @@
           <t>UV International</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>Zone 9 Teynampet</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>044 2621 5907</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>sales@uvinternational.in</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>http://www.uvinternational.in/</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -2001,37 +2013,37 @@
           <t>33AAHFC6849G1ZD</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>Zone 5 Royapuram</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>080 4604 4868</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>chennaiomenterprises@gmail.com</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>http://chennaienterprises.in/</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -2048,32 +2060,32 @@
           <t>33FGRPS5031M1ZS</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>Zone 5 Royapuram</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>089393 44193</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>https://www.chennaiindustrialsuppliers.com/</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -2085,27 +2097,27 @@
           <t>Arvi Hitech Private Limited</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>080 6506 6034</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>ravi@arvihitech.co.in</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -2117,37 +2129,37 @@
           <t>Rane (Madras) Limited - Engine Components Division</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>Zone 10 Kodambakkam</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>044 4297 1800</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>info@ranegroup.com</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>https://ranegroup.com/engine-components-division/</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -2164,32 +2176,32 @@
           <t>33ARUPH9081M1Z0</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>Zone 5 Royapuram</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>076959 69064</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>https://www.kba.co.in/</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -2201,32 +2213,32 @@
           <t>A.M HYDRAULICS &amp; TUBES</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Zone 5 Royapuram</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>093827 13392</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>https://am-hydraulics-tubes.grexa.site/</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -2238,37 +2250,37 @@
           <t>HYDRAULICS &amp; PNEUMATICS SUPPLIERS IN CHENNAI</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>Ward 60</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>098413 92016</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>hapsales52@gmail.com</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>http://www.hydraulicspneumatics.co.in/</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -2285,37 +2297,37 @@
           <t>33AANCS6837K1ZS</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>Zone 7 Ambattur</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>095000 35243</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>samhydromacs@gmail.com</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>http://www.hydromacs.com/</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -2327,37 +2339,37 @@
           <t>Sakthi Era Hydraulic Corporation Pvt. Ltd.</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>Zone 10 Kodambakkam</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>099622 23552</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>sales@sakthieragroup.com</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>http://www.sakthieragroup.com/</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -2369,37 +2381,37 @@
           <t>HINDUSTAN HYDRAULICS &amp; PNEUMATICS</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>Zone 5 Royapuram</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>098409 21885</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>hhp@hindustanhydraulic.in</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>https://www.hindustanhydraulic.com/</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -2411,32 +2423,32 @@
           <t>Madras Cold Forming pvt ltd</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>077080 95226</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>info@madrascoldforming.com</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>https://madrascoldforming.com/</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -2448,32 +2460,32 @@
           <t>ONLINE SAFETY VALVE TESTING - MARABEE TECHNICAL SERVICES</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>070106 90635</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>info@marabee.in</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>http://www.marabee.in/</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -2485,37 +2497,37 @@
           <t>Power Tech Testing and Services</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Zone 7 Ambattur</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>094986 60803</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>enquiry@powertechtesting.com</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>http://powertechtesting.com/</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="P51" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -2532,32 +2544,32 @@
           <t>33AAGFH1389H1ZE</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>Zone 5 Royapuram</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>Valve</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>helpdesk@tradeindia.com</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>https://www.tradeindia.com/hateemy-sales-corporation-15154343/</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="P52" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -2574,52 +2586,52 @@
           <t>29AABCM1475H1ZE</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>Dharmaraya Swamy Temple</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>Bangalore</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>Pump</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>Rahul Goyal</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>080 4896 6770</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>7942818306</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>miecopumps@gmail.com</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>https://www.miecopumps.com/</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -2631,37 +2643,37 @@
           <t>Lubi Industries LLP</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>Pump</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>088844 92629</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>+91-79-61700100</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>bangalore@lubipumps.com</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>https://www.lubipumps.com/contact-us/domestic/bangalore/</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -2673,42 +2685,42 @@
           <t>Kirloskar Pumps</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>Rajajinagar</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>Pump</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>080509 73243</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>+919620159097</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>pumps@bharathdieselgensets.com</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>http://www.kirloskarpumpsdealer.in/</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -2725,42 +2737,42 @@
           <t>29AAICH3961J1Z4</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>SilverJubilee Park Ward</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>Pump</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>070900 94900</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>7799694900</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>info@hablengroup.com</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>https://hablengroup.com/</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="P56" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -2772,42 +2784,42 @@
           <t>Bharat Petroleum Corporation Ltd</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>Vishveshwara Puram</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>Bangalore</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>Pump</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>1800 22 4344</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>9480677382</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>info@bharatpetroleum.in</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>https://www.hellobpcl.in/rolocator/petrol-pumps/bharat-petroleum-petrol-pump-cauvery-auto-service-banglaore-urb-bangalore-104427</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -2819,42 +2831,42 @@
           <t>Sri Sapthagiri Borewell Pumps | Submersible Pump Dealer | Borewell Repair</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>Dharmaraya Swamy Temple Ward</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>Pump</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>086600 44583</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>+91 9342666611</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>support@yourdomain.tld</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>http://srisapthagiriborewellpumps.com/</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="P58" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -2866,42 +2878,42 @@
           <t>Suguna Motors and Pumps</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>SilverJubilee Park Ward</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>Pump</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>080 4114 0765</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>+919448785577</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>Blrsuguna@gmail.com</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>https://nfc.dgtechsoln.com/suguna-motors-pumps/</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="P59" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -2918,42 +2930,42 @@
           <t>29ANNPP3937D1ZM</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>Jagajivanaram Nagar</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>Bangalore</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>Pump</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>080 4895 6017</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>8047823960</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>mca21online@gmail.com</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>http://mahaveerenterprises.in.net/</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="P60" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -2965,47 +2977,47 @@
           <t>KSB Pumps Authorized Dealer - Sri Vishnu Enterprises</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>Cottonpete</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>Pump</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>Cheryl Dunye</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>098451 25944</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>info@srivishnuenterprises.com</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>https://srivishnuenterprises.com/</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="P61" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -3017,42 +3029,42 @@
           <t>Premier Marketing - Grundfos Pumps Sales and Service</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>Dharmaraya Swamy Temple Ward</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>Pump</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>094484 17391</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t>+91-96064 43305</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>sales1@premiermarketing.co.in</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>https://premiermarketing.co.in/</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="P62" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -3064,37 +3076,37 @@
           <t>Shell</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>Basavanagudi</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>Pump</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>074114 80973</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>shellinolimited@gmail.com</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>https://find.shell.com/in/fuel/10055417-bulltemple-road</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -3106,12 +3118,12 @@
           <t>M. Ramaiah &amp; Sons</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>Pump</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="P64" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -3123,42 +3135,42 @@
           <t>Synergy India</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>Dr. Vishnuvardhan Ward</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>Pump</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>098861 12325</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>+08023504805</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>synergyindia.srv@gmail.com</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>http://synergycnppumps.com/</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="P65" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -3170,37 +3182,37 @@
           <t>C S TECHNOLOGY-Automatic Water Level Controller in Bangalore</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>New Tippasandara</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>Bangalore</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>Pump</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t>080953 79069</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t>trans-encoded_email</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t>https://www.cswatertech.com/</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
+      <c r="P66" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -3212,47 +3224,47 @@
           <t>Saptha Innovations Private Limited</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>Malleswaram</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>Pump</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t>095388 69214</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t>+21236547898</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t>service@sapthagroup.com</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="N67" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/saptha-group-37b8851aa/</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="O67" t="inlineStr">
         <is>
           <t>https://www.sapthagroup.com/</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr">
+      <c r="P67" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -3264,17 +3276,17 @@
           <t>Lingala Byraweshwara Nayara petrol pump</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>Pump</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="K68" t="inlineStr">
         <is>
           <t>085533 31441</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
+      <c r="P68" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -3286,22 +3298,22 @@
           <t>Sree Chandra Auto Components pvt ltd</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>Auto components</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t>087544 41041</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr">
+      <c r="O69" t="inlineStr">
         <is>
           <t>http://www.sreechandra.com/index.htm</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr">
+      <c r="P69" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -3313,37 +3325,37 @@
           <t>Aashish Auto Components Manufacturers Private Limited</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>Saidapet</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>Auto components</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t>044 2595 2299</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t>aashishauto@gmail.com</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
+      <c r="O70" t="inlineStr">
         <is>
           <t>http://www.aashishauto.com/</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
+      <c r="P70" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -3355,42 +3367,42 @@
           <t>CHENNAI PUMPS AND SERVICES</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>Zone 13 Adyar</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>Pump</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t>095000 27070</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t>9884075472</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t>sales@chennaipumps.co.in</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr">
+      <c r="O71" t="inlineStr">
         <is>
           <t>http://www.chennaipumps.co.in/</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr">
+      <c r="P71" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -3402,42 +3414,42 @@
           <t>Industrial Pumps Dealer</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>Zone 5 Royapuram</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>Pump</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="K72" t="inlineStr">
         <is>
           <t>+919444212422</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t>+914443012422</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t>sales@chennaipumps.com</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr">
+      <c r="O72" t="inlineStr">
         <is>
           <t>http://www.chennaipumps.com/</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr">
+      <c r="P72" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -3449,37 +3461,37 @@
           <t>Tech Pumps</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>Ward 102</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>Pump</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="K73" t="inlineStr">
         <is>
           <t>098847 46489</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t>info@techpumps.in</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr">
+      <c r="O73" t="inlineStr">
         <is>
           <t>http://www.techpumps.com/</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr">
+      <c r="P73" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -3491,22 +3503,22 @@
           <t>Chennai Pumps Selvi Sanitary And Hardwares Besten Pump, Texmo Pump, Suguna CRI Grundfos Pressure Booster Pump, Finolex</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>Pump</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="K74" t="inlineStr">
         <is>
           <t>095516 27779</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
+      <c r="O74" t="inlineStr">
         <is>
           <t>https://chennaipumps.in/</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr">
+      <c r="P74" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -3518,42 +3530,42 @@
           <t>MTK FAB</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>Zone 11 Valasaravakkam</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>Sheet metal fabrication</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t>099625 08911</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t>+91 9282103429</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t>mtkfab@gmail.com</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="O75" t="inlineStr">
         <is>
           <t>http://www.mtkfab.com/</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
+      <c r="P75" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -3565,37 +3577,37 @@
           <t>Verspanen Engineering Chennai - VMC milling machining Cnc Turning Job work</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>Zone 7 Ambattur</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>CNC job shop</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="K76" t="inlineStr">
         <is>
           <t>097909 79281</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t>Info@verspanen.in</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr">
+      <c r="O76" t="inlineStr">
         <is>
           <t>https://www.verspanen.in/</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr">
+      <c r="P76" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -3607,42 +3619,42 @@
           <t>Hi - Mech Cnc-manufacturer of precision cnc machined components/cnc machining service</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>Zone 7 Ambattur</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>CNC job shop</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="K77" t="inlineStr">
         <is>
           <t>098844 95522</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="L77" t="inlineStr">
         <is>
           <t>+91 98844 95521</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t>senthil@himechcnc.in</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr">
+      <c r="O77" t="inlineStr">
         <is>
           <t>https://himechcnc.in/</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr">
+      <c r="P77" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -3654,42 +3666,42 @@
           <t>Machines Centre</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>Zone 7 Ambattur</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t>CNC job shop</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="K78" t="inlineStr">
         <is>
           <t>098400 52446</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="L78" t="inlineStr">
         <is>
           <t>+91-44-2654 7569</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t>info@machinescentre.com</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr">
+      <c r="O78" t="inlineStr">
         <is>
           <t>https://www.machinescentre.com/</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr">
+      <c r="P78" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -3701,37 +3713,37 @@
           <t>PS Power Controls | Automatic Power Factor Correction Panel | Active Harmonic Filter | Capacitors | EPCOS | L &amp; T | ABB</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>Zone 8 Anna Nagar</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>Electrical panel</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="K79" t="inlineStr">
         <is>
           <t>098408 75082</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t>info@pspowercontrols.com</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr">
+      <c r="O79" t="inlineStr">
         <is>
           <t>http://www.pspowercontrols.com/</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr">
+      <c r="P79" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -3743,37 +3755,37 @@
           <t>GEESYS Technologies India Private Limited</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>Zone 13 Adyar</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>Electrical panel</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="K80" t="inlineStr">
         <is>
           <t>099620 12354</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t>geesyscare@geesysindia.com</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr">
+      <c r="O80" t="inlineStr">
         <is>
           <t>https://www.geesysindia.com/</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr">
+      <c r="P80" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -3785,37 +3797,37 @@
           <t>SAF</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>Zone 3 Madhavaram</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>Foundry (Casting, Alloys, die, Tool die and moulds)</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="K81" t="inlineStr">
         <is>
           <t>073050 74213</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t>sales@southernalloy.org</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr">
+      <c r="O81" t="inlineStr">
         <is>
           <t>http://safindia.com/</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr">
+      <c r="P81" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -3827,42 +3839,42 @@
           <t>Excel Die Castings</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>Ward 164</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>Foundry (Casting, Alloys, die, Tool die and moulds)</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="K82" t="inlineStr">
         <is>
           <t>044 4285 2233</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t>99620 96868</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t>marketing@exceldiecastings.com</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr">
+      <c r="O82" t="inlineStr">
         <is>
           <t>http://www.exceldiecastings.com/</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr">
+      <c r="P82" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -3874,37 +3886,37 @@
           <t>Metals &amp; castings</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>Ward 174</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t>Foundry (Casting, Alloys, die, Tool die and moulds)</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
+      <c r="K83" t="inlineStr">
         <is>
           <t>098403 31364</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t>metals64@gmail.com</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr">
+      <c r="O83" t="inlineStr">
         <is>
           <t>http://www.metalsandcastings.com/</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr">
+      <c r="P83" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -3916,37 +3928,37 @@
           <t>ESP Engineered Components Pvt Ltd</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>Chromepet</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="H84" t="inlineStr">
         <is>
           <t>Engineering (textile engineering components, agriculture engineering components)</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
+      <c r="K84" t="inlineStr">
         <is>
           <t>+91 98400 96474</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
+      <c r="M84" t="inlineStr">
         <is>
           <t>webrequest@espint.com</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr">
+      <c r="O84" t="inlineStr">
         <is>
           <t>http://www.espint.in/</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr">
+      <c r="P84" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -3958,42 +3970,42 @@
           <t>Agricultural Engineering Department</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>Zone 13 Adyar</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="H85" t="inlineStr">
         <is>
           <t>Engineering (textile engineering components, agriculture engineering components)</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
+      <c r="K85" t="inlineStr">
         <is>
           <t>04429510822</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
+      <c r="L85" t="inlineStr">
         <is>
           <t>04429515322</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
+      <c r="M85" t="inlineStr">
         <is>
           <t>aedce.tn@nic.in</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr">
+      <c r="O85" t="inlineStr">
         <is>
           <t>https://aed.tn.gov.in/en/contact-us/</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr">
+      <c r="P85" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -4010,27 +4022,27 @@
           <t>33ALWPB4738M1ZM</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>Kundrathur</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="H86" t="inlineStr">
         <is>
           <t>Engineering (textile engineering components, agriculture engineering components)</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
+      <c r="M86" t="inlineStr">
         <is>
           <t>enterpriseengineeringworks@gmail.com</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr">
+      <c r="O86" t="inlineStr">
         <is>
           <t>https://www.enterpriseengineeringworks.co.in/</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr">
+      <c r="P86" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -4042,37 +4054,37 @@
           <t>Metro Precision Aerospace</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>Zone 8 Anna Nagar</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>Precision (CNC)</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="K87" t="inlineStr">
         <is>
           <t>07397 486 649</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
+      <c r="M87" t="inlineStr">
         <is>
           <t>sales@metroprecision.co.in</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr">
+      <c r="O87" t="inlineStr">
         <is>
           <t>https://www.metroprecision.co.in/,%20%20Instagram:https:%20//www.instagram.com/metro_precision_aerospace?igsh=MWZjcTZ6OWJoODhjYw==,%20%20Youtube:%20https://youtube.com/@metroprecision-123?si=chSU4EfAvqwBcYiF</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr">
+      <c r="P87" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -4084,42 +4096,42 @@
           <t>Precision Machines &amp; Equipments (P) Ltd</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>Ward 137</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="H88" t="inlineStr">
         <is>
           <t>Precision (CNC)</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
+      <c r="K88" t="inlineStr">
         <is>
           <t>099429 94745</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr">
+      <c r="L88" t="inlineStr">
         <is>
           <t>+91-9788230003</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
+      <c r="M88" t="inlineStr">
         <is>
           <t>admin@pmelindia.com;</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr">
+      <c r="O88" t="inlineStr">
         <is>
           <t>http://pmelindia.com/</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr">
+      <c r="P88" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -4131,32 +4143,32 @@
           <t>HILD Defence and Aerospace Pvt Ltd (Operations Office)</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>Defence and Aerospace Components</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
+      <c r="K89" t="inlineStr">
         <is>
           <t>044 4324 1600</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
+      <c r="M89" t="inlineStr">
         <is>
           <t>info@hildad.com</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr">
+      <c r="O89" t="inlineStr">
         <is>
           <t>http://www.hildad.com/</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr">
+      <c r="P89" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -4168,52 +4180,52 @@
           <t>KUN AEROSPACE PRIVATE LIMITED</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>Virapuram</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t>Hanumanthai</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="H90" t="inlineStr">
         <is>
           <t>Defence and Aerospace Components</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t>Mr. G. Srinivasa Rao</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t>CEO</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
+      <c r="K90" t="inlineStr">
         <is>
           <t>098405 18801</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr">
+      <c r="L90" t="inlineStr">
         <is>
           <t>+91 98404 55222</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
+      <c r="M90" t="inlineStr">
         <is>
           <t>gvasu@kunaero.com</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr">
+      <c r="O90" t="inlineStr">
         <is>
           <t>http://www.kunaerospace.com/</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr">
+      <c r="P90" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -4225,52 +4237,52 @@
           <t>Tunga Aerospace Industries Private Limited</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>Zone 13 Adyar</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="H91" t="inlineStr">
         <is>
           <t>Defence and Aerospace Components</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="I91" t="inlineStr">
         <is>
           <t>Cdr Bhaskar</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="J91" t="inlineStr">
         <is>
           <t>CEO</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
+      <c r="K91" t="inlineStr">
         <is>
           <t>+91 9150001591</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr">
+      <c r="L91" t="inlineStr">
         <is>
           <t>+91 9150001590</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
+      <c r="M91" t="inlineStr">
         <is>
           <t>contact@tungasystems.com</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr">
+      <c r="O91" t="inlineStr">
         <is>
           <t>https://tungasystems.com/</t>
         </is>
       </c>
-      <c r="N91" t="inlineStr">
+      <c r="P91" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -4282,32 +4294,32 @@
           <t>AES AUTOMOTIVE COMPANY PRIVATE LIMITED</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>Zone 1 Tiruvottiyur</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="H92" t="inlineStr">
         <is>
           <t>Automotive</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
+      <c r="K92" t="inlineStr">
         <is>
           <t>099406 35250</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
+      <c r="M92" t="inlineStr">
         <is>
           <t>aes270106@yahoo.co.in</t>
         </is>
       </c>
-      <c r="N92" t="inlineStr">
+      <c r="P92" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -4319,42 +4331,42 @@
           <t>Mamta Steel Corporation</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="F93" t="inlineStr">
         <is>
           <t>Zone 7 Ambattur</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="H93" t="inlineStr">
         <is>
           <t>Metal fabrication (sheet, steel, steel wires, steel coil, Press components)</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
+      <c r="K93" t="inlineStr">
         <is>
           <t>091766 71036</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr">
+      <c r="L93" t="inlineStr">
         <is>
           <t>+919840066525</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
+      <c r="M93" t="inlineStr">
         <is>
           <t>mamtasteel2010@gmail.com</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr">
+      <c r="O93" t="inlineStr">
         <is>
           <t>https://mamtasteelcorporation.com/index.php</t>
         </is>
       </c>
-      <c r="N93" t="inlineStr">
+      <c r="P93" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -4366,37 +4378,37 @@
           <t>U-1 Fabrimech Engineers Pvt Ltd</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="H94" t="inlineStr">
         <is>
           <t>Metal fabrication (sheet, steel, steel wires, steel coil, Press components)</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
+      <c r="K94" t="inlineStr">
         <is>
           <t>044 2652 3364</t>
         </is>
       </c>
-      <c r="J94" t="inlineStr">
+      <c r="L94" t="inlineStr">
         <is>
           <t>+91 98407 42321</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
+      <c r="M94" t="inlineStr">
         <is>
           <t>fme@fabrimech.com</t>
         </is>
       </c>
-      <c r="M94" t="inlineStr">
+      <c r="O94" t="inlineStr">
         <is>
           <t>http://www.fabrimech.com/</t>
         </is>
       </c>
-      <c r="N94" t="inlineStr">
+      <c r="P94" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
@@ -4408,52 +4420,46 @@
           <t>SVL Packaging and Printers</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr"/>
-      <c r="C95" t="inlineStr"/>
-      <c r="D95" t="inlineStr">
+      <c r="F95" t="inlineStr">
         <is>
           <t>PN Palayam</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr">
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
         <is>
           <t>093634 56178</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr">
+      <c r="L95" t="inlineStr">
         <is>
           <t>+11002345909</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
+      <c r="M95" t="inlineStr">
         <is>
           <t>svl@support.com</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
+      <c r="O95" t="inlineStr">
         <is>
           <t>https://svlpackaging.com/</t>
         </is>
       </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4461,32 +4467,21 @@
           <t>JEEVI PRINT PACK</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr"/>
-      <c r="C96" t="inlineStr"/>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr">
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
         <is>
           <t>096260 08811</t>
         </is>
       </c>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4494,56 +4489,51 @@
           <t>Surya Graphics</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr"/>
-      <c r="C97" t="inlineStr"/>
-      <c r="D97" t="inlineStr">
+      <c r="F97" t="inlineStr">
         <is>
           <t>Ward 52</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
         <is>
           <t>Reason For Choosing</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
+      <c r="J97" t="inlineStr">
         <is>
           <t>CEO</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
+      <c r="K97" t="inlineStr">
         <is>
           <t>076958 11161</t>
         </is>
       </c>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr">
+      <c r="M97" t="inlineStr">
         <is>
           <t>sales@suryagraphics.in</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
+      <c r="O97" t="inlineStr">
         <is>
           <t>https://suryagraphics.in/</t>
         </is>
       </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4551,44 +4541,36 @@
           <t>Print Leaf</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr"/>
-      <c r="C98" t="inlineStr"/>
-      <c r="D98" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>Patel Nagar</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t>Delhi</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr">
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
         <is>
           <t>087787 00799</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr">
+      <c r="M98" t="inlineStr">
         <is>
           <t>neer.choudhary@hotmail.com</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4601,47 +4583,41 @@
           <t>33BJXPD2473D1Z9</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr"/>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr">
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
         <is>
           <t>099946 22933</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr">
+      <c r="L99" t="inlineStr">
         <is>
           <t>+919698154825</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
+      <c r="M99" t="inlineStr">
         <is>
           <t>qualityprints89@gmail.com</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
+      <c r="O99" t="inlineStr">
         <is>
           <t>https://qualityprinters.co.in/</t>
         </is>
       </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4649,32 +4625,21 @@
           <t>Kanna Papers</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr"/>
-      <c r="C100" t="inlineStr"/>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr">
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
         <is>
           <t>099943 55455</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4682,32 +4647,21 @@
           <t>Kongo Print Packin Pvt. Ltd.</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr"/>
-      <c r="C101" t="inlineStr"/>
-      <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr">
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
         <is>
           <t>0422 421 0323</t>
         </is>
       </c>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4715,32 +4669,21 @@
           <t>Mathy Print Pack</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr"/>
-      <c r="C102" t="inlineStr"/>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr">
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
         <is>
           <t>090035 00104</t>
         </is>
       </c>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4748,56 +4691,51 @@
           <t>High5 Prints - Best Digital Printing Services | Multicolor Printing | Flex Printing In Coimbatore</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr"/>
-      <c r="C103" t="inlineStr"/>
-      <c r="D103" t="inlineStr">
+      <c r="F103" t="inlineStr">
         <is>
           <t>Peelamedu</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="G103" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr">
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
         <is>
           <t>097514 37555</t>
         </is>
       </c>
-      <c r="J103" t="inlineStr">
+      <c r="L103" t="inlineStr">
         <is>
           <t>+91 90422 66862</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
+      <c r="M103" t="inlineStr">
         <is>
           <t>high5prints@gmail.com</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr">
+      <c r="N103" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/high5-prints-54a7691b2/</t>
         </is>
       </c>
-      <c r="M103" t="inlineStr">
+      <c r="O103" t="inlineStr">
         <is>
           <t>http://www.high5prints.in/</t>
         </is>
       </c>
-      <c r="N103" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4805,32 +4743,21 @@
           <t>Mayon Packaging - specialised in paper bags</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr"/>
-      <c r="C104" t="inlineStr"/>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr">
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
         <is>
           <t>077089 88288</t>
         </is>
       </c>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4838,32 +4765,21 @@
           <t>Pro Pack Products</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr"/>
-      <c r="C105" t="inlineStr"/>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
         <is>
           <t>http://propackproducts.in/</t>
         </is>
       </c>
-      <c r="N105" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4871,44 +4787,36 @@
           <t>PK Print F.O.R.M.S – Flex Printing &amp; Foam Boards • Offset • Roll up Standees • Multicolour Printing • Stickers / SunPack</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr"/>
-      <c r="C106" t="inlineStr"/>
-      <c r="D106" t="inlineStr">
+      <c r="F106" t="inlineStr">
         <is>
           <t>Ganapathy</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
+      <c r="G106" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr">
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
         <is>
           <t>077087 98456</t>
         </is>
       </c>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
+      <c r="O106" t="inlineStr">
         <is>
           <t>https://business.google.com/v/_/016050441855450845485/5652/_?caid=17540550924&amp;agid=138846042905</t>
         </is>
       </c>
-      <c r="N106" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4916,48 +4824,41 @@
           <t>Prazasti Print Shop</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr"/>
-      <c r="C107" t="inlineStr"/>
-      <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr">
+      <c r="G107" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr">
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
         <is>
           <t>082700 70006</t>
         </is>
       </c>
-      <c r="J107" t="inlineStr">
+      <c r="L107" t="inlineStr">
         <is>
           <t>4224929192</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
+      <c r="M107" t="inlineStr">
         <is>
           <t>prazastiindia@gmail.com</t>
         </is>
       </c>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
+      <c r="O107" t="inlineStr">
         <is>
           <t>http://www.prazasti.com/</t>
         </is>
       </c>
-      <c r="N107" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4965,56 +4866,51 @@
           <t>Rovaaris Infotech Thermal Paper Roll Manufacturer</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr"/>
-      <c r="C108" t="inlineStr"/>
-      <c r="D108" t="inlineStr">
+      <c r="F108" t="inlineStr">
         <is>
           <t>Ward 21</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
+      <c r="G108" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr">
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
         <is>
           <t>0422 437 2580</t>
         </is>
       </c>
-      <c r="J108" t="inlineStr">
+      <c r="L108" t="inlineStr">
         <is>
           <t>+919894611913</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
+      <c r="M108" t="inlineStr">
         <is>
           <t>varun.rovaaris@gmail.com</t>
         </is>
       </c>
-      <c r="L108" t="inlineStr">
+      <c r="N108" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/rovaaris-infotech-i-pvt-ltd-37417014/?originalSubdomain=in</t>
         </is>
       </c>
-      <c r="M108" t="inlineStr">
+      <c r="O108" t="inlineStr">
         <is>
           <t>http://www.rovaaris.com/</t>
         </is>
       </c>
-      <c r="N108" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5022,48 +4918,41 @@
           <t>Ace Data Prinexcel Pvt. Ltd.</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr"/>
-      <c r="C109" t="inlineStr"/>
-      <c r="D109" t="inlineStr">
+      <c r="F109" t="inlineStr">
         <is>
           <t>Gandhipuram</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
+      <c r="G109" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr">
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
         <is>
           <t>098942 60106</t>
         </is>
       </c>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr">
+      <c r="M109" t="inlineStr">
         <is>
           <t>contact@acedata-india.net</t>
         </is>
       </c>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
+      <c r="O109" t="inlineStr">
         <is>
           <t>http://www.acedata-india.net/Home.html</t>
         </is>
       </c>
-      <c r="N109" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5071,60 +4960,56 @@
           <t>Autoprint Machinery Manufacturers Pvt. Ltd.</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr"/>
-      <c r="C110" t="inlineStr"/>
-      <c r="D110" t="inlineStr">
+      <c r="F110" t="inlineStr">
         <is>
           <t>Choodasandra</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
+      <c r="G110" t="inlineStr">
         <is>
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
         <is>
           <t>Rajashree Ashok</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
+      <c r="J110" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr">
+      <c r="K110" t="inlineStr">
         <is>
           <t>0422 422 5444</t>
         </is>
       </c>
-      <c r="J110" t="inlineStr">
+      <c r="L110" t="inlineStr">
         <is>
           <t>91594 06060</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
+      <c r="M110" t="inlineStr">
         <is>
           <t>info@autoprint.co.in</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
+      <c r="O110" t="inlineStr">
         <is>
           <t>https://www.autoprint.net/?utm_source=googlemaps&amp;utm_medium=organic</t>
         </is>
       </c>
-      <c r="N110" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5132,48 +5017,41 @@
           <t>Print Park</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr"/>
-      <c r="C111" t="inlineStr"/>
-      <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr">
+      <c r="G111" t="inlineStr">
         <is>
           <t>Perumbavoor</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr">
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
         <is>
           <t>090877 11113</t>
         </is>
       </c>
-      <c r="J111" t="inlineStr">
+      <c r="L111" t="inlineStr">
         <is>
           <t>+91 91711 11130</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
+      <c r="M111" t="inlineStr">
         <is>
           <t>admin@printparkgroup.com</t>
         </is>
       </c>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
+      <c r="O111" t="inlineStr">
         <is>
           <t>https://printparkgroup.com/</t>
         </is>
       </c>
-      <c r="N111" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5181,36 +5059,26 @@
           <t>6PROPRINT Packaging Pvt Ltd</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr"/>
-      <c r="C112" t="inlineStr"/>
-      <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr">
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
         <is>
           <t>099448 32845</t>
         </is>
       </c>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
+      <c r="O112" t="inlineStr">
         <is>
           <t>http://www.proprintpackaging.com/</t>
         </is>
       </c>
-      <c r="N112" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5218,32 +5086,21 @@
           <t>Yuga Paper Products (Specialised in Packaging)</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr"/>
-      <c r="C113" t="inlineStr"/>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr"/>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr">
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
         <is>
           <t>084380 86066</t>
         </is>
       </c>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5251,32 +5108,21 @@
           <t>OPAL PRINT N PACK</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr"/>
-      <c r="C114" t="inlineStr"/>
-      <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr">
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
         <is>
           <t>088838 34567</t>
         </is>
       </c>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr"/>
-      <c r="N114" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5284,48 +5130,41 @@
           <t>Maatru Bhoomi</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr"/>
-      <c r="C115" t="inlineStr"/>
-      <c r="D115" t="inlineStr">
+      <c r="F115" t="inlineStr">
         <is>
           <t>Rajendra Nagar</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
+      <c r="G115" t="inlineStr">
         <is>
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr"/>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr">
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
         <is>
           <t>088700 20106</t>
         </is>
       </c>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr">
+      <c r="M115" t="inlineStr">
         <is>
           <t>vishalkodate1912@gmail.com</t>
         </is>
       </c>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
+      <c r="O115" t="inlineStr">
         <is>
           <t>http://www.maatrubhoomi.com/</t>
         </is>
       </c>
-      <c r="N115" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5333,40 +5172,31 @@
           <t>MNR PRINT AND PACKAGING</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr"/>
-      <c r="C116" t="inlineStr"/>
-      <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr">
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
         <is>
           <t>http://+919843060166</t>
         </is>
       </c>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr">
+      <c r="M116" t="inlineStr">
         <is>
           <t>admin@mnrprintandpackaging.com</t>
         </is>
       </c>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
+      <c r="O116" t="inlineStr">
         <is>
           <t>http://www.mnrprintandpackaging.com/</t>
         </is>
       </c>
-      <c r="N116" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -5374,48 +5204,41 @@
           <t>V K ENTERPRISES (Fileman)</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr"/>
-      <c r="C117" t="inlineStr"/>
-      <c r="D117" t="inlineStr"/>
-      <c r="E117" t="inlineStr">
+      <c r="G117" t="inlineStr">
         <is>
           <t>Tiruchanur</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr"/>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr">
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
         <is>
           <t>0422 436 5069</t>
         </is>
       </c>
-      <c r="J117" t="inlineStr">
+      <c r="L117" t="inlineStr">
         <is>
           <t>+91 98422 85269</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
+      <c r="M117" t="inlineStr">
         <is>
           <t>info@filemanindia.com</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
+      <c r="O117" t="inlineStr">
         <is>
           <t>http://www.filemanindia.com/</t>
         </is>
       </c>
-      <c r="N117" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5423,48 +5246,41 @@
           <t>ePrinton</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr"/>
-      <c r="C118" t="inlineStr"/>
-      <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr">
+      <c r="G118" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr">
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
         <is>
           <t>089255 00373</t>
         </is>
       </c>
-      <c r="J118" t="inlineStr">
+      <c r="L118" t="inlineStr">
         <is>
           <t>8044484480</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
+      <c r="M118" t="inlineStr">
         <is>
           <t>info@eprinton.in</t>
         </is>
       </c>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
+      <c r="O118" t="inlineStr">
         <is>
           <t>https://www.eprinton.in/</t>
         </is>
       </c>
-      <c r="N118" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5477,51 +5293,46 @@
           <t>33AVHPM9970D1ZD</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr"/>
-      <c r="D119" t="inlineStr"/>
-      <c r="E119" t="inlineStr">
+      <c r="G119" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr"/>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr">
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
         <is>
           <t>087544 48823</t>
         </is>
       </c>
-      <c r="J119" t="inlineStr">
+      <c r="L119" t="inlineStr">
         <is>
           <t>+918754558823</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
+      <c r="M119" t="inlineStr">
         <is>
           <t>sales@printocare.com.sg</t>
         </is>
       </c>
-      <c r="L119" t="inlineStr">
+      <c r="N119" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/in/murugan-t-3aa0778a?trk=public_profile_samename_profile_profile-result-card_result-card_full-click</t>
         </is>
       </c>
-      <c r="M119" t="inlineStr">
+      <c r="O119" t="inlineStr">
         <is>
           <t>https://www.printocare.com.sg/</t>
         </is>
       </c>
-      <c r="N119" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5529,48 +5340,41 @@
           <t>Vcreate Prints – Premium Digital &amp; Offset Printing Services in Coimbatore</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr"/>
-      <c r="C120" t="inlineStr"/>
-      <c r="D120" t="inlineStr"/>
-      <c r="E120" t="inlineStr">
+      <c r="G120" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr">
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
         <is>
           <t>075400 41555</t>
         </is>
       </c>
-      <c r="J120" t="inlineStr">
+      <c r="L120" t="inlineStr">
         <is>
           <t>+919629229275</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
+      <c r="M120" t="inlineStr">
         <is>
           <t>vcreateprints@gmail.com</t>
         </is>
       </c>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
+      <c r="O120" t="inlineStr">
         <is>
           <t>http://www.vcreateprints.com/</t>
         </is>
       </c>
-      <c r="N120" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5583,55 +5387,51 @@
           <t>33BXFPS1346N1Z5</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr"/>
-      <c r="D121" t="inlineStr">
+      <c r="F121" t="inlineStr">
         <is>
           <t>Ram Nagar</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
+      <c r="G121" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
         <is>
           <t>Ap Murthy</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
+      <c r="J121" t="inlineStr">
         <is>
           <t>CEO</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr">
+      <c r="K121" t="inlineStr">
         <is>
           <t>090039 53554</t>
         </is>
       </c>
-      <c r="J121" t="inlineStr">
+      <c r="L121" t="inlineStr">
         <is>
           <t>8047680201</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
+      <c r="O121" t="inlineStr">
         <is>
           <t>https://www.colorgraphpackaging.com/</t>
         </is>
       </c>
-      <c r="N121" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5639,32 +5439,21 @@
           <t>Kaiser Print Pack</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr"/>
-      <c r="C122" t="inlineStr"/>
-      <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr">
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
         <is>
           <t>096880 07030</t>
         </is>
       </c>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr"/>
-      <c r="N122" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5672,32 +5461,21 @@
           <t>Raam Sai prints</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr"/>
-      <c r="C123" t="inlineStr"/>
-      <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr">
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
         <is>
           <t>063812 94535</t>
         </is>
       </c>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5705,52 +5483,46 @@
           <t>Tekno Prints</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr"/>
-      <c r="C124" t="inlineStr"/>
-      <c r="D124" t="inlineStr">
+      <c r="F124" t="inlineStr">
         <is>
           <t>Gandhipuram</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
+      <c r="G124" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr">
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
         <is>
           <t>093612 87807</t>
         </is>
       </c>
-      <c r="J124" t="inlineStr">
+      <c r="L124" t="inlineStr">
         <is>
           <t>Printing +91-9361287807 Designing : +91 7871287807</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
+      <c r="M124" t="inlineStr">
         <is>
           <t>cbetekno@gmail.com</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
+      <c r="O124" t="inlineStr">
         <is>
           <t>https://www.teknoprints.com/</t>
         </is>
       </c>
-      <c r="N124" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5758,48 +5530,41 @@
           <t>Graphic Solutions</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr"/>
-      <c r="C125" t="inlineStr"/>
-      <c r="D125" t="inlineStr">
+      <c r="F125" t="inlineStr">
         <is>
           <t>Ward 52</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
+      <c r="G125" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr"/>
-      <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr">
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
         <is>
           <t>098942 77112</t>
         </is>
       </c>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr">
+      <c r="M125" t="inlineStr">
         <is>
           <t>info@graphicsolutions.in</t>
         </is>
       </c>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
+      <c r="O125" t="inlineStr">
         <is>
           <t>https://graphicsolutions.in/</t>
         </is>
       </c>
-      <c r="N125" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5807,48 +5572,41 @@
           <t>Pranav Packaging</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr"/>
-      <c r="C126" t="inlineStr"/>
-      <c r="D126" t="inlineStr"/>
-      <c r="E126" t="inlineStr">
+      <c r="G126" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr"/>
-      <c r="H126" t="inlineStr"/>
-      <c r="I126" t="inlineStr">
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
         <is>
           <t>094433 37593</t>
         </is>
       </c>
-      <c r="J126" t="inlineStr">
+      <c r="L126" t="inlineStr">
         <is>
           <t>+91 78455 55155</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr">
+      <c r="M126" t="inlineStr">
         <is>
           <t>pranavpackaging@gmail.com</t>
         </is>
       </c>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
+      <c r="O126" t="inlineStr">
         <is>
           <t>http://www.pranavpackaging.com/</t>
         </is>
       </c>
-      <c r="N126" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5861,51 +5619,46 @@
           <t>33CEGPS1702B1Z3</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr"/>
-      <c r="D127" t="inlineStr">
+      <c r="F127" t="inlineStr">
         <is>
           <t>Ward 45</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
+      <c r="G127" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr"/>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr">
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
         <is>
           <t>095977 43986</t>
         </is>
       </c>
-      <c r="J127" t="inlineStr">
+      <c r="L127" t="inlineStr">
         <is>
           <t>8940660600</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
+      <c r="M127" t="inlineStr">
         <is>
           <t>%20md.ftctissues@gmail.com</t>
         </is>
       </c>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
+      <c r="O127" t="inlineStr">
         <is>
           <t>https://www.ftcpapermachine.com/</t>
         </is>
       </c>
-      <c r="N127" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5913,32 +5666,21 @@
           <t>Arun Packaging Industries</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr"/>
-      <c r="C128" t="inlineStr"/>
-      <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr"/>
-      <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr">
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
         <is>
           <t>0422 253 1978</t>
         </is>
       </c>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr"/>
-      <c r="N128" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5946,48 +5688,41 @@
           <t>Rishaba Poly Packs</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr"/>
-      <c r="C129" t="inlineStr"/>
-      <c r="D129" t="inlineStr"/>
-      <c r="E129" t="inlineStr">
+      <c r="G129" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr"/>
-      <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr">
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
         <is>
           <t>0422 436 1717</t>
         </is>
       </c>
-      <c r="J129" t="inlineStr">
+      <c r="L129" t="inlineStr">
         <is>
           <t>+91 73737 12345</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr">
+      <c r="M129" t="inlineStr">
         <is>
           <t>rishabhapolypack@gmail.com</t>
         </is>
       </c>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
+      <c r="O129" t="inlineStr">
         <is>
           <t>https://rishabagroup.com/poly-products-manufacturer-in-coimbatore.php</t>
         </is>
       </c>
-      <c r="N129" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5995,40 +5730,31 @@
           <t>A S Packaging</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr"/>
-      <c r="C130" t="inlineStr"/>
-      <c r="D130" t="inlineStr"/>
-      <c r="E130" t="inlineStr">
+      <c r="G130" t="inlineStr">
         <is>
           <t>Ahmedabad</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr">
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
         <is>
           <t>079043 41988</t>
         </is>
       </c>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr">
+      <c r="M130" t="inlineStr">
         <is>
           <t>manoj_nair@intaspharma.com</t>
         </is>
       </c>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O130" t="inlineStr"/>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -6036,52 +5762,46 @@
           <t>Vidiyal Offset Printers</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr"/>
-      <c r="C131" t="inlineStr"/>
-      <c r="D131" t="inlineStr">
+      <c r="F131" t="inlineStr">
         <is>
           <t>PN Palayam</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
+      <c r="G131" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr"/>
-      <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr">
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
         <is>
           <t>095976 05888</t>
         </is>
       </c>
-      <c r="J131" t="inlineStr">
+      <c r="L131" t="inlineStr">
         <is>
           <t>0422%20496%202929</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr">
+      <c r="M131" t="inlineStr">
         <is>
           <t>vidiyaloffsetprinters2023@gmail.com</t>
         </is>
       </c>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
+      <c r="O131" t="inlineStr">
         <is>
           <t>https://www.vidiyaloffsetprinters.com/</t>
         </is>
       </c>
-      <c r="N131" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O131" t="inlineStr"/>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -6089,48 +5809,41 @@
           <t>PHOENIX CARTONS (Corrugated, Duplex Cartons Box Manufacturer)</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr"/>
-      <c r="C132" t="inlineStr"/>
-      <c r="D132" t="inlineStr">
+      <c r="F132" t="inlineStr">
         <is>
           <t>Ward 61</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
+      <c r="G132" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr"/>
-      <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr">
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
         <is>
           <t>084383 77559</t>
         </is>
       </c>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr">
+      <c r="M132" t="inlineStr">
         <is>
           <t>info@phoenixcartons.com</t>
         </is>
       </c>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
+      <c r="O132" t="inlineStr">
         <is>
           <t>https://www.phoenixcartons.com/</t>
         </is>
       </c>
-      <c r="N132" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O132" t="inlineStr"/>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -6138,44 +5851,36 @@
           <t>Art KG</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr"/>
-      <c r="C133" t="inlineStr"/>
-      <c r="D133" t="inlineStr"/>
-      <c r="E133" t="inlineStr">
+      <c r="G133" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr"/>
-      <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr">
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
         <is>
           <t>078454 76996</t>
         </is>
       </c>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr">
+      <c r="M133" t="inlineStr">
         <is>
           <t>artkg.kailash@gmail.com</t>
         </is>
       </c>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
+      <c r="O133" t="inlineStr">
         <is>
           <t>http://www.artkg.in/</t>
         </is>
       </c>
-      <c r="N133" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O133" t="inlineStr"/>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -6183,36 +5888,26 @@
           <t>Meena Printing Works</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr"/>
-      <c r="C134" t="inlineStr"/>
-      <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr"/>
-      <c r="H134" t="inlineStr"/>
-      <c r="I134" t="inlineStr">
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
         <is>
           <t>096297 33330</t>
         </is>
       </c>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
+      <c r="O134" t="inlineStr">
         <is>
           <t>http://www.meenaprintingworks.in/</t>
         </is>
       </c>
-      <c r="N134" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O134" t="inlineStr"/>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -6220,44 +5915,36 @@
           <t>Packobags</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr"/>
-      <c r="C135" t="inlineStr"/>
-      <c r="D135" t="inlineStr"/>
-      <c r="E135" t="inlineStr">
+      <c r="G135" t="inlineStr">
         <is>
           <t>Bokaro</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr"/>
-      <c r="H135" t="inlineStr"/>
-      <c r="I135" t="inlineStr">
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
         <is>
           <t>090436 07000</t>
         </is>
       </c>
-      <c r="J135" t="inlineStr">
+      <c r="L135" t="inlineStr">
         <is>
           <t>+91 86681 12340</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
+      <c r="O135" t="inlineStr">
         <is>
           <t>https://www.packobags.com/</t>
         </is>
       </c>
-      <c r="N135" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O135" t="inlineStr"/>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -6265,48 +5952,41 @@
           <t>Giftery - Fancy Gifts Items | Stationary | Engraving and Customized Gifts | Personalized Gifts | Toys</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr"/>
-      <c r="C136" t="inlineStr"/>
-      <c r="D136" t="inlineStr"/>
-      <c r="E136" t="inlineStr">
+      <c r="G136" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr"/>
-      <c r="I136" t="inlineStr">
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
         <is>
           <t>080150 76749</t>
         </is>
       </c>
-      <c r="J136" t="inlineStr">
+      <c r="L136" t="inlineStr">
         <is>
           <t>+91 70101 21945</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr">
+      <c r="M136" t="inlineStr">
         <is>
           <t>giftery2023@gmail.com</t>
         </is>
       </c>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
+      <c r="O136" t="inlineStr">
         <is>
           <t>http://www.gifterys.com/</t>
         </is>
       </c>
-      <c r="N136" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O136" t="inlineStr"/>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -6314,44 +5994,36 @@
           <t>Chithralekhaa Printers - Corrugated box &amp; Carton Box</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr"/>
-      <c r="C137" t="inlineStr"/>
-      <c r="D137" t="inlineStr"/>
-      <c r="E137" t="inlineStr">
+      <c r="G137" t="inlineStr">
         <is>
           <t>Chettipalayam</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr"/>
-      <c r="H137" t="inlineStr"/>
-      <c r="I137" t="inlineStr">
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
         <is>
           <t>086753 61477</t>
         </is>
       </c>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr">
+      <c r="M137" t="inlineStr">
         <is>
           <t>chithralekhaaprinters@gmail.com</t>
         </is>
       </c>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
+      <c r="O137" t="inlineStr">
         <is>
           <t>https://chithralekhaaprinters.com/</t>
         </is>
       </c>
-      <c r="N137" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O137" t="inlineStr"/>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -6359,48 +6031,41 @@
           <t>CHITTAL PAPER COMPANY</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr"/>
-      <c r="C138" t="inlineStr"/>
-      <c r="D138" t="inlineStr"/>
-      <c r="E138" t="inlineStr">
+      <c r="G138" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr"/>
-      <c r="H138" t="inlineStr"/>
-      <c r="I138" t="inlineStr">
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
         <is>
           <t>090030 97052</t>
         </is>
       </c>
-      <c r="J138" t="inlineStr">
+      <c r="L138" t="inlineStr">
         <is>
           <t>9840173134</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr">
+      <c r="M138" t="inlineStr">
         <is>
           <t>kasichittal@gmail.com</t>
         </is>
       </c>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
+      <c r="O138" t="inlineStr">
         <is>
           <t>http://www.chittal.com/</t>
         </is>
       </c>
-      <c r="N138" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O138" t="inlineStr"/>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -6413,51 +6078,46 @@
           <t>33AAMFC2987N1ZU</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr"/>
-      <c r="D139" t="inlineStr">
+      <c r="F139" t="inlineStr">
         <is>
           <t>Ward 28</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
+      <c r="G139" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr"/>
-      <c r="H139" t="inlineStr"/>
-      <c r="I139" t="inlineStr">
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
         <is>
           <t>097515 02447</t>
         </is>
       </c>
-      <c r="J139" t="inlineStr">
+      <c r="L139" t="inlineStr">
         <is>
           <t>+919994274133</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr">
+      <c r="M139" t="inlineStr">
         <is>
           <t>createcpack@gmail.com</t>
         </is>
       </c>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
+      <c r="O139" t="inlineStr">
         <is>
           <t>https://createcpack.com/</t>
         </is>
       </c>
-      <c r="N139" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O139" t="inlineStr"/>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -6465,52 +6125,46 @@
           <t>Dream Dots Print Pack</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr"/>
-      <c r="C140" t="inlineStr"/>
-      <c r="D140" t="inlineStr">
+      <c r="F140" t="inlineStr">
         <is>
           <t>Uppilipalayam</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
+      <c r="G140" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr"/>
-      <c r="H140" t="inlineStr"/>
-      <c r="I140" t="inlineStr">
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
         <is>
           <t>088834 11144</t>
         </is>
       </c>
-      <c r="J140" t="inlineStr">
+      <c r="L140" t="inlineStr">
         <is>
           <t>+91 99945 11144</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr">
+      <c r="M140" t="inlineStr">
         <is>
           <t>print@dreamdots.in, dreamdots.print@gmail.com, dreamdots.acc@gmail.com</t>
         </is>
       </c>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
+      <c r="O140" t="inlineStr">
         <is>
           <t>http://www.dreamdots.in/</t>
         </is>
       </c>
-      <c r="N140" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O140" t="inlineStr"/>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -6518,52 +6172,46 @@
           <t>MS Prints</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr"/>
-      <c r="C141" t="inlineStr"/>
-      <c r="D141" t="inlineStr">
+      <c r="F141" t="inlineStr">
         <is>
           <t>Ward 9</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
+      <c r="G141" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr"/>
-      <c r="H141" t="inlineStr"/>
-      <c r="I141" t="inlineStr">
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
         <is>
           <t>090037 67867</t>
         </is>
       </c>
-      <c r="J141" t="inlineStr">
+      <c r="L141" t="inlineStr">
         <is>
           <t>+919514734000</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr">
+      <c r="M141" t="inlineStr">
         <is>
           <t>msprintscbe@gmail.com</t>
         </is>
       </c>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
+      <c r="O141" t="inlineStr">
         <is>
           <t>http://msprints.in/</t>
         </is>
       </c>
-      <c r="N141" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O141" t="inlineStr"/>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -6571,36 +6219,26 @@
           <t>Sri Sastha Engineering</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr"/>
-      <c r="C142" t="inlineStr"/>
-      <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr"/>
-      <c r="H142" t="inlineStr"/>
-      <c r="I142" t="inlineStr">
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
         <is>
           <t>080 4803 0567</t>
         </is>
       </c>
-      <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
+      <c r="O142" t="inlineStr">
         <is>
           <t>https://www.srisasthaengineering.co.in/</t>
         </is>
       </c>
-      <c r="N142" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O142" t="inlineStr"/>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -6613,47 +6251,41 @@
           <t>33AOOPM1228C1ZB</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr"/>
-      <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr">
+      <c r="G143" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr"/>
-      <c r="H143" t="inlineStr"/>
-      <c r="I143" t="inlineStr">
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
         <is>
           <t>094478 14433</t>
         </is>
       </c>
-      <c r="J143" t="inlineStr">
+      <c r="L143" t="inlineStr">
         <is>
           <t>08045815953</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr">
+      <c r="M143" t="inlineStr">
         <is>
           <t>marketing@sampackindia.com</t>
         </is>
       </c>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
+      <c r="O143" t="inlineStr">
         <is>
           <t>http://www.sampack.in/</t>
         </is>
       </c>
-      <c r="N143" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -6661,32 +6293,21 @@
           <t>Inmac Innovations</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr"/>
-      <c r="C144" t="inlineStr"/>
-      <c r="D144" t="inlineStr"/>
-      <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr"/>
-      <c r="H144" t="inlineStr"/>
-      <c r="I144" t="inlineStr">
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
         <is>
           <t>099943 82331</t>
         </is>
       </c>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr"/>
-      <c r="N144" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -6694,52 +6315,46 @@
           <t>INTERO PACTEC INDIA PVT LTD</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr"/>
-      <c r="C145" t="inlineStr"/>
-      <c r="D145" t="inlineStr">
+      <c r="F145" t="inlineStr">
         <is>
           <t>Ward 94</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr">
+      <c r="G145" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr"/>
-      <c r="I145" t="inlineStr">
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
         <is>
           <t>093618 77345</t>
         </is>
       </c>
-      <c r="J145" t="inlineStr">
+      <c r="L145" t="inlineStr">
         <is>
           <t>+91 9843232104</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr">
+      <c r="M145" t="inlineStr">
         <is>
           <t>interopactec@gmail.com</t>
         </is>
       </c>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
+      <c r="O145" t="inlineStr">
         <is>
           <t>https://www.interopactec.com/</t>
         </is>
       </c>
-      <c r="N145" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -6747,48 +6362,41 @@
           <t>VELMAYIL ENTERPRISES - வேல்மயில் எண்டர்பிரைஸஸ்</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr"/>
-      <c r="C146" t="inlineStr"/>
-      <c r="D146" t="inlineStr"/>
-      <c r="E146" t="inlineStr">
+      <c r="G146" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr"/>
-      <c r="I146" t="inlineStr">
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
         <is>
           <t>098422 16456</t>
         </is>
       </c>
-      <c r="J146" t="inlineStr">
+      <c r="L146" t="inlineStr">
         <is>
           <t>+91-98428 18419</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr">
+      <c r="M146" t="inlineStr">
         <is>
           <t>info@velmayil.com</t>
         </is>
       </c>
-      <c r="L146" t="inlineStr"/>
-      <c r="M146" t="inlineStr">
+      <c r="O146" t="inlineStr">
         <is>
           <t>http://www.velmayil.com/</t>
         </is>
       </c>
-      <c r="N146" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O146" t="inlineStr"/>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -6796,52 +6404,46 @@
           <t>Vimala Paper Company</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr"/>
-      <c r="C147" t="inlineStr"/>
-      <c r="D147" t="inlineStr">
+      <c r="F147" t="inlineStr">
         <is>
           <t>Balarengapuram</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr">
+      <c r="G147" t="inlineStr">
         <is>
           <t>Madurai</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr"/>
-      <c r="I147" t="inlineStr">
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
         <is>
           <t>0422 239 0022</t>
         </is>
       </c>
-      <c r="J147" t="inlineStr">
+      <c r="L147" t="inlineStr">
         <is>
           <t>//+91 9952430533</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr">
+      <c r="M147" t="inlineStr">
         <is>
           <t>info@vimala.in</t>
         </is>
       </c>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
+      <c r="O147" t="inlineStr">
         <is>
           <t>http://www.vimala.in/</t>
         </is>
       </c>
-      <c r="N147" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O147" t="inlineStr"/>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -6849,40 +6451,31 @@
           <t>HANDY</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr"/>
-      <c r="C148" t="inlineStr"/>
-      <c r="D148" t="inlineStr"/>
-      <c r="E148" t="inlineStr">
+      <c r="G148" t="inlineStr">
         <is>
           <t>Rohtak</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr">
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
         <is>
           <t>097888 47738</t>
         </is>
       </c>
-      <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr">
+      <c r="M148" t="inlineStr">
         <is>
           <t>gulia.rahul@gmail.com</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr"/>
-      <c r="N148" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -6890,36 +6483,26 @@
           <t>Zig Zag Art Printers</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr"/>
-      <c r="C149" t="inlineStr"/>
-      <c r="D149" t="inlineStr"/>
-      <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr"/>
-      <c r="H149" t="inlineStr"/>
-      <c r="I149" t="inlineStr">
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
         <is>
           <t>0422 437 1166</t>
         </is>
       </c>
-      <c r="J149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
+      <c r="O149" t="inlineStr">
         <is>
           <t>http://zigzagadmin.com/</t>
         </is>
       </c>
-      <c r="N149" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O149" t="inlineStr"/>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -6927,32 +6510,21 @@
           <t>Paper cover machine</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr"/>
-      <c r="C150" t="inlineStr"/>
-      <c r="D150" t="inlineStr"/>
-      <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr"/>
-      <c r="H150" t="inlineStr"/>
-      <c r="I150" t="inlineStr">
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
         <is>
           <t>093679 79777</t>
         </is>
       </c>
-      <c r="J150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr"/>
-      <c r="N150" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O150" t="inlineStr"/>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -6960,36 +6532,26 @@
           <t>SCUBE PRINTS</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr"/>
-      <c r="C151" t="inlineStr"/>
-      <c r="D151" t="inlineStr"/>
-      <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr"/>
-      <c r="H151" t="inlineStr"/>
-      <c r="I151" t="inlineStr">
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
         <is>
           <t>097892 22299</t>
         </is>
       </c>
-      <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
+      <c r="O151" t="inlineStr">
         <is>
           <t>https://www.scubeprints.in/</t>
         </is>
       </c>
-      <c r="N151" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O151" t="inlineStr"/>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -6997,52 +6559,46 @@
           <t>Unique India Paper Teknix</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr"/>
-      <c r="C152" t="inlineStr"/>
-      <c r="D152" t="inlineStr">
+      <c r="F152" t="inlineStr">
         <is>
           <t>Bharathi Nagar</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr">
+      <c r="G152" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr"/>
-      <c r="H152" t="inlineStr"/>
-      <c r="I152" t="inlineStr">
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
         <is>
           <t>091235 31499</t>
         </is>
       </c>
-      <c r="J152" t="inlineStr">
+      <c r="L152" t="inlineStr">
         <is>
           <t>08048031809</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr">
+      <c r="M152" t="inlineStr">
         <is>
           <t>sales@uniqueindiapaperteknix.com</t>
         </is>
       </c>
-      <c r="L152" t="inlineStr"/>
-      <c r="M152" t="inlineStr">
+      <c r="O152" t="inlineStr">
         <is>
           <t>https://www.uniqueindiapaperteknix.net/</t>
         </is>
       </c>
-      <c r="N152" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O152" t="inlineStr"/>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -7050,48 +6606,41 @@
           <t>Rainbow Printers</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr"/>
-      <c r="C153" t="inlineStr"/>
-      <c r="D153" t="inlineStr">
+      <c r="F153" t="inlineStr">
         <is>
           <t>Andheri East</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr">
+      <c r="G153" t="inlineStr">
         <is>
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr"/>
-      <c r="H153" t="inlineStr"/>
-      <c r="I153" t="inlineStr">
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
         <is>
           <t>098945 03030</t>
         </is>
       </c>
-      <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr">
+      <c r="M153" t="inlineStr">
         <is>
           <t>hemnani68@hotmail.com</t>
         </is>
       </c>
-      <c r="L153" t="inlineStr"/>
-      <c r="M153" t="inlineStr">
+      <c r="O153" t="inlineStr">
         <is>
           <t>https://rainbowfy.in/</t>
         </is>
       </c>
-      <c r="N153" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O153" t="inlineStr"/>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -7104,43 +6653,36 @@
           <t>33BAWPS6765F1ZZ</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr"/>
-      <c r="D154" t="inlineStr"/>
-      <c r="E154" t="inlineStr">
+      <c r="G154" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr"/>
-      <c r="H154" t="inlineStr"/>
-      <c r="I154" t="inlineStr">
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
         <is>
           <t>090037 57800</t>
         </is>
       </c>
-      <c r="J154" t="inlineStr">
+      <c r="L154" t="inlineStr">
         <is>
           <t>8047523179</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
-      <c r="L154" t="inlineStr"/>
-      <c r="M154" t="inlineStr">
+      <c r="O154" t="inlineStr">
         <is>
           <t>https://www.swamypackaging.in/</t>
         </is>
       </c>
-      <c r="N154" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O154" t="inlineStr"/>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -7148,32 +6690,21 @@
           <t>Sri Sakthi Promotional Litho Process</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr"/>
-      <c r="C155" t="inlineStr"/>
-      <c r="D155" t="inlineStr"/>
-      <c r="E155" t="inlineStr"/>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr"/>
-      <c r="H155" t="inlineStr"/>
-      <c r="I155" t="inlineStr">
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
         <is>
           <t>0422 240 3500</t>
         </is>
       </c>
-      <c r="J155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
-      <c r="L155" t="inlineStr"/>
-      <c r="M155" t="inlineStr"/>
-      <c r="N155" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O155" t="inlineStr"/>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -7181,32 +6712,21 @@
           <t>Craftyvok</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr"/>
-      <c r="C156" t="inlineStr"/>
-      <c r="D156" t="inlineStr"/>
-      <c r="E156" t="inlineStr"/>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr"/>
-      <c r="H156" t="inlineStr"/>
-      <c r="I156" t="inlineStr">
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
         <is>
           <t>096298 84220</t>
         </is>
       </c>
-      <c r="J156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
-      <c r="M156" t="inlineStr"/>
-      <c r="N156" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O156" t="inlineStr"/>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -7214,32 +6734,21 @@
           <t>Sai Vaidya Traders</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr"/>
-      <c r="C157" t="inlineStr"/>
-      <c r="D157" t="inlineStr"/>
-      <c r="E157" t="inlineStr"/>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr"/>
-      <c r="H157" t="inlineStr"/>
-      <c r="I157" t="inlineStr">
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
         <is>
           <t>098947 66504</t>
         </is>
       </c>
-      <c r="J157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
-      <c r="M157" t="inlineStr"/>
-      <c r="N157" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O157" t="inlineStr"/>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -7252,47 +6761,41 @@
           <t>33ABVFS7327L1ZF</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr"/>
-      <c r="D158" t="inlineStr">
+      <c r="F158" t="inlineStr">
         <is>
           <t>Bharathi Nagar</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr">
+      <c r="G158" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr"/>
-      <c r="H158" t="inlineStr"/>
-      <c r="I158" t="inlineStr">
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
         <is>
           <t>099445 25500</t>
         </is>
       </c>
-      <c r="J158" t="inlineStr">
+      <c r="L158" t="inlineStr">
         <is>
           <t>7949358094</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr">
+      <c r="O158" t="inlineStr">
         <is>
           <t>http://www.saptthagiri.com/</t>
         </is>
       </c>
-      <c r="N158" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O158" t="inlineStr"/>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -7300,52 +6803,46 @@
           <t>Dhisan Packaging Solution</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr"/>
-      <c r="C159" t="inlineStr"/>
-      <c r="D159" t="inlineStr"/>
-      <c r="E159" t="inlineStr">
+      <c r="G159" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
         <is>
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
+      <c r="J159" t="inlineStr">
         <is>
           <t>MD</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr">
+      <c r="K159" t="inlineStr">
         <is>
           <t>095859 77727</t>
         </is>
       </c>
-      <c r="J159" t="inlineStr"/>
-      <c r="K159" t="inlineStr">
+      <c r="M159" t="inlineStr">
         <is>
           <t>info@dhisanpackaging.com</t>
         </is>
       </c>
-      <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
+      <c r="O159" t="inlineStr">
         <is>
           <t>http://dhisanpackaging.com/</t>
         </is>
       </c>
-      <c r="N159" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O159" t="inlineStr"/>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -7353,44 +6850,36 @@
           <t>Covai Cottons Jute Bags manufacture In Coimbatore</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr"/>
-      <c r="C160" t="inlineStr"/>
-      <c r="D160" t="inlineStr"/>
-      <c r="E160" t="inlineStr"/>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr"/>
-      <c r="H160" t="inlineStr"/>
-      <c r="I160" t="inlineStr">
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
         <is>
           <t>098946 99968</t>
         </is>
       </c>
-      <c r="J160" t="inlineStr">
+      <c r="L160" t="inlineStr">
         <is>
           <t>+919843755333</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr">
+      <c r="M160" t="inlineStr">
         <is>
           <t>covaicottons@gmail.com</t>
         </is>
       </c>
-      <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
+      <c r="O160" t="inlineStr">
         <is>
           <t>http://covaicottons.com/</t>
         </is>
       </c>
-      <c r="N160" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O160" t="inlineStr"/>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -7398,28 +6887,16 @@
           <t>Keerthi Printers</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr"/>
-      <c r="C161" t="inlineStr"/>
-      <c r="D161" t="inlineStr"/>
-      <c r="E161" t="inlineStr"/>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr"/>
-      <c r="H161" t="inlineStr"/>
-      <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr"/>
-      <c r="M161" t="inlineStr"/>
-      <c r="N161" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O161" t="inlineStr"/>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -7427,36 +6904,26 @@
           <t>AASHIRVAAD CARDS (Exclusive &amp; Wholesale Shop)</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr"/>
-      <c r="C162" t="inlineStr"/>
-      <c r="D162" t="inlineStr"/>
-      <c r="E162" t="inlineStr"/>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr"/>
-      <c r="H162" t="inlineStr"/>
-      <c r="I162" t="inlineStr">
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
         <is>
           <t>099443 32587</t>
         </is>
       </c>
-      <c r="J162" t="inlineStr"/>
-      <c r="K162" t="inlineStr"/>
-      <c r="L162" t="inlineStr"/>
-      <c r="M162" t="inlineStr">
+      <c r="O162" t="inlineStr">
         <is>
           <t>http://www.aashirvaadcardsdesigns.com/</t>
         </is>
       </c>
-      <c r="N162" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O162" t="inlineStr"/>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -7464,32 +6931,21 @@
           <t>ESSAR BAGS</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr"/>
-      <c r="C163" t="inlineStr"/>
-      <c r="D163" t="inlineStr"/>
-      <c r="E163" t="inlineStr"/>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr"/>
-      <c r="H163" t="inlineStr"/>
-      <c r="I163" t="inlineStr">
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
         <is>
           <t>098430 80184</t>
         </is>
       </c>
-      <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr"/>
-      <c r="L163" t="inlineStr"/>
-      <c r="M163" t="inlineStr"/>
-      <c r="N163" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O163" t="inlineStr"/>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -7497,36 +6953,26 @@
           <t>Mahaveer Papers</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr"/>
-      <c r="C164" t="inlineStr"/>
-      <c r="D164" t="inlineStr"/>
-      <c r="E164" t="inlineStr"/>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr"/>
-      <c r="H164" t="inlineStr"/>
-      <c r="I164" t="inlineStr">
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
         <is>
           <t>099940 12149</t>
         </is>
       </c>
-      <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
-      <c r="L164" t="inlineStr"/>
-      <c r="M164" t="inlineStr">
+      <c r="O164" t="inlineStr">
         <is>
           <t>https://mahaveerpapers.in/</t>
         </is>
       </c>
-      <c r="N164" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O164" t="inlineStr"/>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -7534,32 +6980,21 @@
           <t>Autoprint Press</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr"/>
-      <c r="C165" t="inlineStr"/>
-      <c r="D165" t="inlineStr"/>
-      <c r="E165" t="inlineStr"/>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr"/>
-      <c r="H165" t="inlineStr"/>
-      <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
-      <c r="M165" t="inlineStr">
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
         <is>
           <t>https://www.autoprintpress.com/</t>
         </is>
       </c>
-      <c r="N165" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O165" t="inlineStr"/>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -7567,52 +7002,46 @@
           <t>Unicom Infotel Pvt Ltd</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr"/>
-      <c r="C166" t="inlineStr"/>
-      <c r="D166" t="inlineStr">
+      <c r="F166" t="inlineStr">
         <is>
           <t>Powai</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr">
+      <c r="G166" t="inlineStr">
         <is>
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr"/>
-      <c r="H166" t="inlineStr"/>
-      <c r="I166" t="inlineStr">
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
         <is>
           <t>0422 421 4302</t>
         </is>
       </c>
-      <c r="J166" t="inlineStr">
+      <c r="L166" t="inlineStr">
         <is>
           <t>8108108540</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr">
+      <c r="M166" t="inlineStr">
         <is>
           <t>response@unicominfotel.com</t>
         </is>
       </c>
-      <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr">
+      <c r="O166" t="inlineStr">
         <is>
           <t>http://www.unicominfotel.com/</t>
         </is>
       </c>
-      <c r="N166" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O166" t="inlineStr"/>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -7620,52 +7049,46 @@
           <t>Chromaprint India Private Limited | IML Label Manufacturer | Pressure Sensitive | Wet Glue | Shrink Sleeve | IML</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr"/>
-      <c r="C167" t="inlineStr"/>
-      <c r="D167" t="inlineStr">
+      <c r="F167" t="inlineStr">
         <is>
           <t>Nagar Road</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr">
+      <c r="G167" t="inlineStr">
         <is>
           <t>Pune</t>
         </is>
       </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr"/>
-      <c r="H167" t="inlineStr"/>
-      <c r="I167" t="inlineStr">
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
         <is>
           <t>0422 264 2738</t>
         </is>
       </c>
-      <c r="J167" t="inlineStr">
+      <c r="L167" t="inlineStr">
         <is>
           <t>+918610495165</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr">
+      <c r="M167" t="inlineStr">
         <is>
           <t>info@chromaprintindia.com</t>
         </is>
       </c>
-      <c r="L167" t="inlineStr"/>
-      <c r="M167" t="inlineStr">
+      <c r="O167" t="inlineStr">
         <is>
           <t>http://www.chromaprintindia.com/</t>
         </is>
       </c>
-      <c r="N167" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O167" t="inlineStr"/>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -7673,36 +7096,26 @@
           <t>Pie bags Pvt. Ltd.,</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr"/>
-      <c r="C168" t="inlineStr"/>
-      <c r="D168" t="inlineStr"/>
-      <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr"/>
-      <c r="H168" t="inlineStr"/>
-      <c r="I168" t="inlineStr">
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
         <is>
           <t>098432 66139</t>
         </is>
       </c>
-      <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr">
+      <c r="O168" t="inlineStr">
         <is>
           <t>https://www.piebags.in/</t>
         </is>
       </c>
-      <c r="N168" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O168" t="inlineStr"/>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -7710,44 +7123,36 @@
           <t>Senthur Printers</t>
         </is>
       </c>
-      <c r="B169" t="inlineStr"/>
-      <c r="C169" t="inlineStr"/>
-      <c r="D169" t="inlineStr"/>
-      <c r="E169" t="inlineStr">
+      <c r="G169" t="inlineStr">
         <is>
           <t>Daman</t>
         </is>
       </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr"/>
-      <c r="H169" t="inlineStr"/>
-      <c r="I169" t="inlineStr">
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
         <is>
           <t>098940 49627</t>
         </is>
       </c>
-      <c r="J169" t="inlineStr"/>
-      <c r="K169" t="inlineStr">
+      <c r="M169" t="inlineStr">
         <is>
           <t>info@senthurprinters.com</t>
         </is>
       </c>
-      <c r="L169" t="inlineStr"/>
-      <c r="M169" t="inlineStr">
+      <c r="O169" t="inlineStr">
         <is>
           <t>https://www.senthurprinters.com/</t>
         </is>
       </c>
-      <c r="N169" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O169" t="inlineStr"/>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -7755,44 +7160,36 @@
           <t>InkDeMemories</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr"/>
-      <c r="C170" t="inlineStr"/>
-      <c r="D170" t="inlineStr"/>
-      <c r="E170" t="inlineStr">
+      <c r="G170" t="inlineStr">
         <is>
           <t>Arjuni Morgaon</t>
         </is>
       </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr"/>
-      <c r="H170" t="inlineStr"/>
-      <c r="I170" t="inlineStr">
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
         <is>
           <t>097901 63564</t>
         </is>
       </c>
-      <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr">
+      <c r="M170" t="inlineStr">
         <is>
           <t>inkdememories@gmail.com</t>
         </is>
       </c>
-      <c r="L170" t="inlineStr"/>
-      <c r="M170" t="inlineStr">
+      <c r="O170" t="inlineStr">
         <is>
           <t>https://inkdememories.com/</t>
         </is>
       </c>
-      <c r="N170" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O170" t="inlineStr"/>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -7800,44 +7197,36 @@
           <t>The Print Panda - Custom Tshirt, DTF printing &amp; Embroidery</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr"/>
-      <c r="C171" t="inlineStr"/>
-      <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr">
+      <c r="G171" t="inlineStr">
         <is>
           <t>Tiruchirappalli</t>
         </is>
       </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr"/>
-      <c r="H171" t="inlineStr"/>
-      <c r="I171" t="inlineStr">
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
         <is>
           <t>086680 85103</t>
         </is>
       </c>
-      <c r="J171" t="inlineStr">
+      <c r="L171" t="inlineStr">
         <is>
           <t>+917996607996</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
-      <c r="L171" t="inlineStr"/>
-      <c r="M171" t="inlineStr">
+      <c r="O171" t="inlineStr">
         <is>
           <t>http://corporate.theprintpanda.com/</t>
         </is>
       </c>
-      <c r="N171" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O171" t="inlineStr"/>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -7845,52 +7234,46 @@
           <t>Priadharsini Wedding Cards</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr"/>
-      <c r="C172" t="inlineStr"/>
-      <c r="D172" t="inlineStr">
+      <c r="F172" t="inlineStr">
         <is>
           <t>Ram Nagar</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr">
+      <c r="G172" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr"/>
-      <c r="H172" t="inlineStr"/>
-      <c r="I172" t="inlineStr">
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
         <is>
           <t>096002 13999</t>
         </is>
       </c>
-      <c r="J172" t="inlineStr">
+      <c r="L172" t="inlineStr">
         <is>
           <t>+91 9994620999</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr">
+      <c r="M172" t="inlineStr">
         <is>
           <t>priyacards@gmail.com</t>
         </is>
       </c>
-      <c r="L172" t="inlineStr"/>
-      <c r="M172" t="inlineStr">
+      <c r="O172" t="inlineStr">
         <is>
           <t>https://www.priyacards.com/</t>
         </is>
       </c>
-      <c r="N172" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O172" t="inlineStr"/>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -7903,47 +7286,41 @@
           <t>33AAIFN9961D1Z4</t>
         </is>
       </c>
-      <c r="C173" t="inlineStr"/>
-      <c r="D173" t="inlineStr">
+      <c r="F173" t="inlineStr">
         <is>
           <t>Ward 52</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr">
+      <c r="G173" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr"/>
-      <c r="H173" t="inlineStr"/>
-      <c r="I173" t="inlineStr">
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
         <is>
           <t>080 4606 8931</t>
         </is>
       </c>
-      <c r="J173" t="inlineStr">
+      <c r="L173" t="inlineStr">
         <is>
           <t>7942671643</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
-      <c r="L173" t="inlineStr"/>
-      <c r="M173" t="inlineStr">
+      <c r="O173" t="inlineStr">
         <is>
           <t>https://www.ntprintingsolutions.in/</t>
         </is>
       </c>
-      <c r="N173" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O173" t="inlineStr"/>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -7951,36 +7328,26 @@
           <t>AA Enterprises</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr"/>
-      <c r="C174" t="inlineStr"/>
-      <c r="D174" t="inlineStr"/>
-      <c r="E174" t="inlineStr">
+      <c r="G174" t="inlineStr">
         <is>
           <t>Noida</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr"/>
-      <c r="H174" t="inlineStr"/>
-      <c r="I174" t="inlineStr"/>
-      <c r="J174" t="inlineStr"/>
-      <c r="K174" t="inlineStr">
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
         <is>
           <t>Info.mgfx@gmail.com</t>
         </is>
       </c>
-      <c r="L174" t="inlineStr"/>
-      <c r="M174" t="inlineStr"/>
-      <c r="N174" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O174" t="inlineStr"/>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -7988,52 +7355,46 @@
           <t>Y2P</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr"/>
-      <c r="C175" t="inlineStr"/>
-      <c r="D175" t="inlineStr">
+      <c r="F175" t="inlineStr">
         <is>
           <t>Venkatapura</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr">
+      <c r="G175" t="inlineStr">
         <is>
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr"/>
-      <c r="H175" t="inlineStr"/>
-      <c r="I175" t="inlineStr">
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
         <is>
           <t>098422 18888</t>
         </is>
       </c>
-      <c r="J175" t="inlineStr">
+      <c r="L175" t="inlineStr">
         <is>
           <t>+919047054546</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr">
+      <c r="M175" t="inlineStr">
         <is>
           <t>sales@yes2print.com</t>
         </is>
       </c>
-      <c r="L175" t="inlineStr"/>
-      <c r="M175" t="inlineStr">
+      <c r="O175" t="inlineStr">
         <is>
           <t>http://www.yes2print.com/</t>
         </is>
       </c>
-      <c r="N175" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O175" t="inlineStr"/>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -8041,32 +7402,21 @@
           <t>Sivasalapathy digitals</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr"/>
-      <c r="C176" t="inlineStr"/>
-      <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr"/>
-      <c r="H176" t="inlineStr"/>
-      <c r="I176" t="inlineStr">
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
         <is>
           <t>096557 75828</t>
         </is>
       </c>
-      <c r="J176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
-      <c r="L176" t="inlineStr"/>
-      <c r="M176" t="inlineStr"/>
-      <c r="N176" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O176" t="inlineStr"/>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -8079,51 +7429,46 @@
           <t>33BRIPS6214C1Z0</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr"/>
-      <c r="D177" t="inlineStr">
+      <c r="F177" t="inlineStr">
         <is>
           <t>Ganapathy</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr">
+      <c r="G177" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr"/>
-      <c r="H177" t="inlineStr"/>
-      <c r="I177" t="inlineStr">
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
         <is>
           <t>099948 67519</t>
         </is>
       </c>
-      <c r="J177" t="inlineStr">
+      <c r="L177" t="inlineStr">
         <is>
           <t>7942653107</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr">
+      <c r="M177" t="inlineStr">
         <is>
           <t>info@safeittech.com</t>
         </is>
       </c>
-      <c r="L177" t="inlineStr"/>
-      <c r="M177" t="inlineStr">
+      <c r="O177" t="inlineStr">
         <is>
           <t>https://www.safesolution.co.in/</t>
         </is>
       </c>
-      <c r="N177" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O177" t="inlineStr"/>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -8131,32 +7476,21 @@
           <t>St.Joseph Graphix</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr"/>
-      <c r="C178" t="inlineStr"/>
-      <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr"/>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr"/>
-      <c r="H178" t="inlineStr"/>
-      <c r="I178" t="inlineStr">
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
         <is>
           <t>087781 92989</t>
         </is>
       </c>
-      <c r="J178" t="inlineStr"/>
-      <c r="K178" t="inlineStr"/>
-      <c r="L178" t="inlineStr"/>
-      <c r="M178" t="inlineStr"/>
-      <c r="N178" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O178" t="inlineStr"/>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -8164,32 +7498,21 @@
           <t>Sri Saravana Printers | Screen printer | Coimbatore</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr"/>
-      <c r="C179" t="inlineStr"/>
-      <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr"/>
-      <c r="H179" t="inlineStr"/>
-      <c r="I179" t="inlineStr">
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
         <is>
           <t>096776 60829</t>
         </is>
       </c>
-      <c r="J179" t="inlineStr"/>
-      <c r="K179" t="inlineStr"/>
-      <c r="L179" t="inlineStr"/>
-      <c r="M179" t="inlineStr"/>
-      <c r="N179" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O179" t="inlineStr"/>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -8197,48 +7520,41 @@
           <t>PRINTECH MACHINERIES</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr"/>
-      <c r="C180" t="inlineStr"/>
-      <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr">
+      <c r="G180" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr"/>
-      <c r="H180" t="inlineStr"/>
-      <c r="I180" t="inlineStr">
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
         <is>
           <t>096295 35100</t>
         </is>
       </c>
-      <c r="J180" t="inlineStr">
+      <c r="L180" t="inlineStr">
         <is>
           <t>+91 7418353854</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr">
+      <c r="M180" t="inlineStr">
         <is>
           <t>printechcbe@yahoo.co.in</t>
         </is>
       </c>
-      <c r="L180" t="inlineStr"/>
-      <c r="M180" t="inlineStr">
+      <c r="O180" t="inlineStr">
         <is>
           <t>https://www.printechcbe.com/</t>
         </is>
       </c>
-      <c r="N180" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O180" t="inlineStr"/>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -8246,60 +7562,56 @@
           <t>Tints &amp; Shades Co.</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr"/>
-      <c r="C181" t="inlineStr"/>
-      <c r="D181" t="inlineStr">
+      <c r="F181" t="inlineStr">
         <is>
           <t>Ward 136</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr">
+      <c r="G181" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
         <is>
           <t>Chief Executive Officer</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
+      <c r="J181" t="inlineStr">
         <is>
           <t>CEO</t>
         </is>
       </c>
-      <c r="I181" t="inlineStr">
+      <c r="K181" t="inlineStr">
         <is>
           <t>079040 02343</t>
         </is>
       </c>
-      <c r="J181" t="inlineStr">
+      <c r="L181" t="inlineStr">
         <is>
           <t>+917904002343%20</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr">
+      <c r="M181" t="inlineStr">
         <is>
           <t>tintsnshadesco@gmail.com</t>
         </is>
       </c>
-      <c r="L181" t="inlineStr"/>
-      <c r="M181" t="inlineStr">
+      <c r="O181" t="inlineStr">
         <is>
           <t>https://tintsnshadesco.com/</t>
         </is>
       </c>
-      <c r="N181" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O181" t="inlineStr"/>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -8307,48 +7619,41 @@
           <t>Boson Packaging</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr"/>
-      <c r="C182" t="inlineStr"/>
-      <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr">
+      <c r="G182" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr"/>
-      <c r="H182" t="inlineStr"/>
-      <c r="I182" t="inlineStr">
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
         <is>
           <t>098404 55500</t>
         </is>
       </c>
-      <c r="J182" t="inlineStr">
+      <c r="L182" t="inlineStr">
         <is>
           <t>+919791699061</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr">
+      <c r="M182" t="inlineStr">
         <is>
           <t>info@bosonpackaging.in</t>
         </is>
       </c>
-      <c r="L182" t="inlineStr"/>
-      <c r="M182" t="inlineStr">
+      <c r="O182" t="inlineStr">
         <is>
           <t>http://bosonpackaging.in/</t>
         </is>
       </c>
-      <c r="N182" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O182" t="inlineStr"/>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -8356,32 +7661,21 @@
           <t>Green Tech Paper Products</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr"/>
-      <c r="C183" t="inlineStr"/>
-      <c r="D183" t="inlineStr"/>
-      <c r="E183" t="inlineStr"/>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr"/>
-      <c r="H183" t="inlineStr"/>
-      <c r="I183" t="inlineStr">
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
         <is>
           <t>090879 23339</t>
         </is>
       </c>
-      <c r="J183" t="inlineStr"/>
-      <c r="K183" t="inlineStr"/>
-      <c r="L183" t="inlineStr"/>
-      <c r="M183" t="inlineStr"/>
-      <c r="N183" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O183" t="inlineStr"/>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -8389,31 +7683,408 @@
           <t>Adya Print and Packaging</t>
         </is>
       </c>
-      <c r="B184" t="inlineStr"/>
-      <c r="C184" t="inlineStr"/>
-      <c r="D184" t="inlineStr"/>
-      <c r="E184" t="inlineStr"/>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>Paper, printing and packaging</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr"/>
-      <c r="H184" t="inlineStr"/>
-      <c r="I184" t="inlineStr"/>
-      <c r="J184" t="inlineStr"/>
-      <c r="K184" t="inlineStr"/>
-      <c r="L184" t="inlineStr"/>
-      <c r="M184" t="inlineStr"/>
-      <c r="N184" t="inlineStr">
-        <is>
-          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
-        </is>
-      </c>
-      <c r="O184" t="inlineStr"/>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Paper, printing and packaging</t>
+        </is>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Aira India Automation</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr"/>
+      <c r="C185" t="inlineStr"/>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Ward 97 Somajiguda</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Valve</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>097277 21063</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>9346110773</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>hyderabad@airaindia.com</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr"/>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>https://hyderabad.airaindia.com/</t>
+        </is>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Industria Needs - Industrial Valves, Ball Valves, Butterfly Valves, Globe Valves, Gate Valves in Hyderabad</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr"/>
+      <c r="C186" t="inlineStr"/>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Ward 148 Ramgopalpet</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Valve</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>093910 28747</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>+919133011392</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>industrianeeds@gmail.com</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr"/>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>https://www.industrianeeds.com/</t>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>ITCENGCO</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr"/>
+      <c r="C187" t="inlineStr"/>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Banjara Hills</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Valve</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Mr Urmil Dharia</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>098851 21394</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>+91 9246915626</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>Urmildharia.itcengco@gmail.com</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/in/urmil-dharia-b0620856</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>https://itcengco.com/</t>
+        </is>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Stanvalves and Controls Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr"/>
+      <c r="C188" t="inlineStr"/>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Ward 130 Subash Nagar</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Valve</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>087126 95383</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>+918978580683</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>sales@stanvalves.com</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr"/>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>https://www.stanvalves.com/</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Vulcan Valves</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr"/>
+      <c r="C189" t="inlineStr"/>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Somajiguda</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Valve</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>040 2980 0855</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>hrd@vulcanvalves.com</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr"/>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>http://vulcanvalves.com/</t>
+        </is>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+      <c r="Q189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Grow-wel Hydraulics</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr"/>
+      <c r="C190" t="inlineStr"/>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Ward 149 Begumpet</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Valve</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>099496 58686</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>+91 9391035987</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>growwelhyd@gmail.com</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr"/>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>http://www.growwelhydraulics.com/</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>ROYAL METAL INDUSTRIES</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr"/>
+      <c r="C191" t="inlineStr"/>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Ward 148 Ramgopalpet</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Valve</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>075693 45965</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>royalmetalhyd@gmail.com</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr"/>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>http://www.royalmetalgroup.in/</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O184"/>
+  <autoFilter ref="A1:Q191"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/backend/exports/All_Extracted_Leads.xlsx
+++ b/backend/exports/All_Extracted_Leads.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6936" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="LeadCommonImportDTO" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="__lead_export_mapping__" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LeadCommonImportDTO" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="__lead_export_mapping__" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'LeadCommonImportDTO'!$A$1:$P$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'LeadCommonImportDTO'!$A$1:$P$94</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -930,7 +930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P94"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.88671875" defaultRowHeight="12" customHeight="1"/>
   <cols>
     <col width="11.109375" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
@@ -1126,11 +1126,6 @@
           <t>ELVEE AUTOS Petrol pump (CNG AVAILABLE)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Nagapattinam - Coimbatore - Gundlupet Hwy</t>
@@ -1141,17 +1136,11 @@
           <t>Poondi</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1164,32 +1153,21 @@
           <t>MADHURA AGENCY (MULTI BRAND)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>077080 07075</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>Saravana Tiles, 224/6 ARRS Multiplex Road, Sangeetha mobile upstair, near, New Bus Stand Rd</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1202,32 +1180,21 @@
           <t>Salem Pipe Traders</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>0422 238 7696</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>King's Complex, 343, Dr Nanjapaa Rd</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1240,28 +1207,16 @@
           <t>IMPACT FURNITURE</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>New Delhi</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1274,11 +1229,6 @@
           <t>DEODAP</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>Plot No. 93-94, Riana Tower, 2nd Floor</t>
@@ -1289,17 +1239,11 @@
           <t>Indore</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
           <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1312,10 +1256,6 @@
           <t>IDENTIQA INTERIORS PRIVATE LIMITED</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>bkgarg200402@gmail.com</t>
@@ -1331,17 +1271,11 @@
           <t>Gurgaon</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
           <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1354,15 +1288,11 @@
           <t>TNEB SUPERINTENDING ENGINEEROFFICE</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>0427 224 4282</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>M654+R8R, Salem Bypass, Post</t>
@@ -1373,17 +1303,11 @@
           <t>Salem</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
           <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1396,15 +1320,11 @@
           <t>Shanthi Enterprises (Texmo Industries - Authorised Sales And Service in Salem)</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>094430 98247</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>Skandha Towers, 363, CC Rd</t>
@@ -1415,17 +1335,11 @@
           <t>Madiki</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1438,15 +1352,11 @@
           <t>Salem LOA Bunk</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>0427 222 5232</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>NH 44</t>
@@ -1457,17 +1367,11 @@
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1480,32 +1384,21 @@
           <t>C.R.I PUMPS SERVICE CENTRE</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>097888 32220</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>SRI VINAYAGA MOTOR SERVICE CENTRE 131/11, PANANGADU, Meyyanur Main Rd</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
           <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1518,9 +1411,6 @@
           <t>Salem Corporation Ammapet Zonal Office</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>0427 225 0300</t>
@@ -1536,18 +1426,11 @@
           <t>M55G+6V9</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
           <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1560,24 +1443,11 @@
           <t>Bharat Petroleum, Petrol Pump -Rowther &amp; Co</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
           <t>unverified: industry not supplied; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1590,24 +1460,11 @@
           <t>Bharat Petroleum, Petrol Pump -Subramaniyam Pillai Traders</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
           <t>unverified: industry not supplied; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1620,28 +1477,16 @@
           <t>Bharat Petroleum, Petrol Pump -K.S.K Agencies</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>094432 31881</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
           <t>unverified: industry not supplied; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1654,11 +1499,6 @@
           <t>Vao Office</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>1-Feb, Chinnakadai St</t>
@@ -1669,17 +1509,11 @@
           <t>Tirukkoyilur</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
           <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1692,11 +1526,6 @@
           <t>RKF Motors &amp; Pumps and Pipes Salem (Since 1960)</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>No 12, RK Foundry complex, Chittu Koil St</t>
@@ -1707,17 +1536,11 @@
           <t>Delhi</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
           <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1730,10 +1553,6 @@
           <t>Modern Agencies</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>mrchechi21@rediffmail.com</t>
@@ -1749,17 +1568,11 @@
           <t>Tirur</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
           <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1772,15 +1585,11 @@
           <t>Bharat Petroleum, Petrol Pump - Sowdambiga Fuels</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>070944 66677</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>3/53, Trichy Main Rd</t>
@@ -1791,17 +1600,11 @@
           <t>Thanjavur</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1814,9 +1617,6 @@
           <t>GOKULAM ENGINEERING STORES &amp; SERVICE</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>098427 04321</t>
@@ -1837,20 +1637,2272 @@
           <t>Salem</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
           <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Globle Electricals- Electrical Contractors/Panel Board Manufacturers &amp; Suppliers/Electrical Goods</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>099948 57966</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>No: 31/A Thiruvagoundanur By Pass</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SRI RANGA TECH</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>095007 51833</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>jrnganesh@gmail.com</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>D.no- 12-18-5 Siddivinayaka Nagar, Phool Bagh Vizianagaram Vizianagaram Andhra Pradesh - 535002</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Vizianagaram</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>VL ELECTRICAL</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>098944 43325</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>123/5, Itteri Rd, Meyyanur, Salem, Tamil Nadu • 636004, Itteri Rd</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Baladiya</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Vardhaman Electricals</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>083009 55944</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>vardhamanelectricals5@gmail.com</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>42, 6/15, SWAMI VIVEKANAND NAGAR, NEAR JIJAMATA NAGAR, DR. E MOSES ROAD, WORLI MUMBAI Mumbai City Maharashtra - 400018</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Knowledge Electronics</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>093455 17455</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>1st Floor, Chinnammal Complex ARRS Multiplex Road, New Bus Stand Rd, near Apple I planet</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Ongole</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>GENERAL ELECTRICAL AND ELECTRONIC SOLUTIONS</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>099444 20014</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>unverified: industry not supplied; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Elite Energy Devices</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>093611 92261</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>unverified: industry not supplied; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>System Control</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>094881 89406</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>office2854@gmail.com</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>B/203 VASTUJ R MHATRE MARG JUHU MUMBAI Maharashtra - 400049</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Sri Krishna Electrical Company</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Bus Stand, No 46/1 , Chittu Pillayar kovil street Old</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Kolkata</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Salem Electricals</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>096555 60882</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>M537+772, 11/1, Pochin Rd</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Kolkata</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Bharat Power Engineer</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>098427 43128</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>517/1, 5 Rd</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Salem electricals &amp;hardware</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>J5VG+7XX, Bye Ln</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Domjur</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Sathya Motors &amp; Electricals</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>099441 49965</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>M49F+55J Sri Vani Mahal Thirumana Mandapam, Thiruvagoundanur, Bypass</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BALAJI ELECTRICALS (Plumbing,Lighting&amp;Sanitaryware)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>096295 56641</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>NO 9/4, Near, New Bus Stand Rd, opp. to G.R Residency</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Jaygaon</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Adritya Systems- Leading solar Dealer Salem</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>096558 96373</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>130/182-A, 2nd Agraharam</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>POWER HOUSE EQUIPMENT</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>063825 29206</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>st.gautam@gmail.com</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>76/117, Military Rd</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Sree Ramakrishna Electricals</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>0427 226 5701</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>4, Kallanguthu St</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Puducherry</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>SRI PADMAVATHI ELECTRICALS</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Leigh Bazaar, 251-3, East Coast Rd</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Pudupattanam</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Kanvika Hardwares and Electricals</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>099423 48733</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Thiru v.k road</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ABI ELECTRONICS- best cable tv service center SALEM</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>088832 86888</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>unverified: industry not supplied; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>DHARSHAN TRADERS</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>098944 58585</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>dharshanindiatraders@gmail.com</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>6/207B, MIMISAL ROAD, AVUDIYARKOIL, Tirupperunthurai, Pudukkottai, Avudayarkoil, Tamil Nadu, India, 614618 - 614618</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Pudukkottai</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Poorvika Appliances Salem</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>044 4366 6666</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Survey No. 58/1B2A, Meyyanur By Pass Road ARRS Theatre Side, Street Corner</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Pigeon Exclusive Store - LRN Colony, Salem | Chimneys, Hobs, Cast Iron Cookware &amp; More</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>0427 355 6835</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>23, Sarada College Rd, beside Pepes The Great Sleep</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>P.V. Electricals</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>094432 73449</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>pkanandelec@yahoo.com</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>H-17 EAST CHANDER NAGARGALI NO-7 DELHI Delhi - 110052</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Salem steel house</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>098434 12342</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2164, 2167, Nagapattinam - Coimbatore - Gundlupet Hwy</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Poondi</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>SALEM STAINLESS STEEL SUPPLIERS PVT LTD</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>2/1, 1st Cross Road, KK Nagar, Police Quarters Rd</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Sarjapura</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Salem Steel Corporation</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>098424 32057</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>27, Arutchelvar Dr N Mahalingam Rd</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Salem Steel Plant- SAIL</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>unverified: industry not supplied; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Select Steels</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0427 244 3011</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>selectsteels@gmail.com</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>61-B PALM AVENUEP S KARAYA KOLKATA West Bengal - 700019</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Kolkata</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Golden Steel Corporation</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>0427 235 2662</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>rajnish1961@yahoo.com</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>18/1B Loudon Street Park Street Kolkata Kolkata West Bengal - 700016</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Kolkata</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Salem Steel Kothu karanty Sri Balaji Steels gorimedu</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>098653 62489</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>636008</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Kannankurichi</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Salem Kamalam Steel</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>090470 61816</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>S.F.No :15/1, SBI Officers Colony, 2 Cross, Service Rd, near AVR Circle</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>RJM STEELS SALEM</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>080155 20670</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>unverified: industry not supplied; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Indian Steel Company in Salem</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>095145 35458</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>41, Seetharam Rd</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Kolkata</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Trichy Steel Company</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>228-B, Suramangalam Main Rd</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>185 RD-B</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>SALEM STEEL PLANT</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>unverified: industry not supplied; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>South India Steel Company</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>073734 07700</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Ts 44&amp;45, Cuddalore Main Rd</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>SRI KARTHIKEYAN INDUSTRIES (Steel furniture manufacturing and fabrication)</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>085240 42665</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Bus Stop, 239 V.o.c nagar colony, Ammapet colony</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Colony</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Kaveri Steel</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>098428 88041</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>MALHOTRA HOUSE, 5TH. FLOOR,OPP. GPO, BOMBAY-1. Maharashtra - 000000</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Bhattian Bet</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Aishwarya Steel Industries</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>183, kumaragiripettai</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Bidhannagar</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Mercury Steels Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>073587 71115</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>49/2A, Bye Pass</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Barrage</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Sri Balaji Industries</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>094436 21886</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>105, Cuddalore Main Rd</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Sri Valarmathi Industry</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>098430 76288</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>44, pattanakiyar kadu</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Kadu</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Basha Steel Pipes JSW Roofing sheets TMT Structurals Dealer Salem</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>093623 52256</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>M45X+M78, 3</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Chakravarthi Steels</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>088705 56677</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Lakshmi Nagar, 134, Omalur Main Rd, near National Hotel</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Salem Steel Plant Road</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>150, Cuddalore Main Rd, near Vasan Eye Care</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Puducherry</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Sri Valarmathi Furnitures &amp; valarmathi industry</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>098430 76288</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>158, Cuddalore Main Rd</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Vijay Steel Works</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>098947 56758</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>9, Seetharam Rd</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Ghaziabad</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Sri Ramajayam Iron &amp; Steel</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>30, CSI Building, Fort Main Rd</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Bellary</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Grundfos Pressure Pump distributor Salem | Sana Ventures</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>098403 67550</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>sales@sanaventures.co.in</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>180,Ganesh Buildings, Chinnaswamy Naidu Road, New Siddhapudur (Near Omni Busstand), Coimbatore-641044.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Indore</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>SAKTI MURUGAN TRADERS ( C.R.I.PUMPS DEALER)</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>098427 50546</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Murugan Complex, 70/68, Chittu Kovil Street Sakthi, Kallanguthu St</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Aqua Motor Agencies (Authorised dealer exclusively for TEXMO motors and pumps)</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>098427 62177</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>47, Arunachala Asari Street</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Bharat Petroleum</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>094426 31956</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>kameshwarprasad@bharatpetroleum.in</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Sanjay Khanna	Chairman &amp; Managing Director with Addl. Charge of Director (Refineries)	BPCL, Bharat Bhavan, 4 &amp; 6 Currimbhoy Road, Ballard Estate, Mumbai 400001	+91 02222713000 / +91 02222714000	cmd[at]bharatpetroleum[dot]in</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Grundfos Service Center</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>091597 87878</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>134/5-2, By Pass, opp. to RTO Office</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Mira-Bhayandar</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Bharat Petrol Pump</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>AMMAPET</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Ammapet</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Madeena Diesel Pump Service</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>098427 23624</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>No.27, Samzo Complex, F.F Road Opp M.R.Engine Reborin Dadhubaikuttai</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Vadodara</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Meckwell Engineers</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>094434 14986</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>15, CC Rd, near Old Bus Stand Road</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Samy Traders Bharat Petroleum</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>094432 59808</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Salem - Ulundurpettai Hwy</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Apps Trading Conpany V Market</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>No.3, Mel Bose Maithanam</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>No.3 Siruani</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Concentric Engineers</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>091122 50670</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Survey No. 32/3/2, Danny Mehata Industrial Area, Near Khadi Machine Chowk behind Hotel Angaraj, Kondhwa, Yewalewadi Rd</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>27AAUPM1630Q1Z0</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Kirloskar Ebara Pumps Ltd</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Sai Residency Banglows, Baner Rd</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>27AAACK7293A1ZN</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>500 Crore</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Hacop Pumps</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Ravindra Gadre</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>084080 33553</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>hacoppumps@gmail.com</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>A-1, SR 1, Hissa 6+22+B-1, B- wing, Raje Manor Apartments, Hingane BK, Karvenagar PUNE Pune Maharashtra - 411052</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>27AAACH6378P1ZV</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>50 Lakh</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Right from transportation and distribution of water</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Mr. Girish Dharmadhikari</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>087939 95743</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>sales4@punepumps.com</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Flat 6, Ameya Apartment, Anantkrupa Society, Janata Sahakari Bank Lane, Opposite Samartha Hotel Shivtirth Nagar, Kothrud Pune – 411038</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Aditi Engineering</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>020 2443 0306</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>info.aditiglobal@gmail.com</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>FF03 1ST FL GOKULAM AVENU, VALLALAR SALAI EXTN SARAM, Saram(Py), Pondicherry, Pondicherry, Pondicherry, India, 605013 - 605013</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>27AYDPS4072P1ZQ</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>50 Lakh</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>P K Shah&amp;Sons</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>086685 86792</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>vikasshah42@gmail.com</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>250, near Akra Maruti Kopara, Shukrawar Peth, Pune, Maharashtra 411002, India</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>HOSUR STEEL INDUSTRIES</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>33AAKPK6082G1ZO</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>50 Lakh</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>unverified: industry not supplied; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>BARANI STEELS</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>098427 90564</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>No 2, Matham Rd, opp. Park</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Hosur</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>33AAKFB6099A1ZL</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>1 Lakh</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: employee count unavailable</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>STEEL ENGINEERING ENTERPRISES - FOUNDRY</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>SIPCOT Industrial Complex, 55-A</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Hosur</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Naveen Industrial Corporation (Alloy Steels/Tool Steels/Die Steels)</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>E-13(Part), SIDCO Industrial Estate</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Banashankari Pipes Pvt Ltd. Hosur Branch</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>093613 22822</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>privacy@teaminternet.com</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>No:53A, Denkanikottai Rd, Near TNSTC/SETC Bus depot</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>IBCC Industries India Private Limited</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>04144 865 460</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>ASLAM.MOHAMMAD@IBCC-INDIA.COM</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>B-16A and B-17, GALLOPS INDUSTRIAL PARK, PHASE-I NATIONAL HIGHWAY NO. 8A ROAD, RAJODA BAVLA Gujarat - 382220</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>24AAFCI5058Q1Z2</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P23"/>
+  <autoFilter ref="A1:P94"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
 </worksheet>

--- a/backend/exports/All_Extracted_Leads.xlsx
+++ b/backend/exports/All_Extracted_Leads.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="__lead_export_mapping__" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'LeadCommonImportDTO'!$A$1:$P$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'LeadCommonImportDTO'!$A$1:$P$156</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -930,20 +930,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P94"/>
+  <dimension ref="A1:P156"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.88671875" defaultRowHeight="12" customHeight="1"/>
   <cols>
     <col width="11.109375" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
     <col width="50" customWidth="1" style="2" min="2" max="2"/>
     <col width="28.44140625" customWidth="1" style="2" min="3" max="3"/>
     <col width="29.5546875" customWidth="1" style="3" min="4" max="4"/>
-    <col width="16.44140625" customWidth="1" style="2" min="5" max="5"/>
+    <col width="19" customWidth="1" style="2" min="5" max="5"/>
     <col width="32.44140625" customWidth="1" style="1" min="6" max="6"/>
     <col width="44.5546875" customWidth="1" style="2" min="7" max="7"/>
     <col width="50" customWidth="1" style="2" min="8" max="8"/>
     <col width="29.21875" customWidth="1" style="2" min="9" max="9"/>
     <col width="20.5546875" customWidth="1" style="2" min="10" max="10"/>
-    <col width="23.109375" customWidth="1" style="2" min="11" max="11"/>
+    <col width="25" customWidth="1" style="2" min="11" max="11"/>
     <col width="50" customWidth="1" style="2" min="12" max="12"/>
     <col width="15.5546875" customWidth="1" style="2" min="13" max="13"/>
     <col width="21.109375" customWidth="1" style="2" min="14" max="14"/>
@@ -3664,13 +3664,6 @@
           <t>HOSUR STEEL INDUSTRIES</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr"/>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
           <t>33AAKPK6082G1ZO</t>
@@ -3686,10 +3679,6 @@
           <t>unverified: industry not supplied; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
-      <c r="P89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3702,15 +3691,11 @@
           <t>BARANI STEELS</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
           <t>098427 90564</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
           <t>No 2, Matham Rd, opp. Park</t>
@@ -3736,10 +3721,6 @@
           <t>unverified: declared industry could not be matched to a target segment; unverified: employee count unavailable</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
-      <c r="P90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3752,11 +3733,6 @@
           <t>STEEL ENGINEERING ENTERPRISES - FOUNDRY</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
           <t>SIPCOT Industrial Complex, 55-A</t>
@@ -3767,17 +3743,11 @@
           <t>Hosur</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
-      <c r="P91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3790,28 +3760,16 @@
           <t>Naveen Industrial Corporation (Alloy Steels/Tool Steels/Die Steels)</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
           <t>E-13(Part), SIDCO Industrial Estate</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
         <is>
           <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
-      <c r="O92" t="inlineStr"/>
-      <c r="P92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3824,9 +3782,6 @@
           <t>Banashankari Pipes Pvt Ltd. Hosur Branch</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr"/>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
           <t>093613 22822</t>
@@ -3842,18 +3797,11 @@
           <t>No:53A, Denkanikottai Rd, Near TNSTC/SETC Bus depot</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
           <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
-      <c r="P93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3866,9 +3814,6 @@
           <t>IBCC Industries India Private Limited</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr"/>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
           <t>04144 865 460</t>
@@ -3884,25 +3829,2223 @@
           <t>B-16A and B-17, GALLOPS INDUSTRIAL PARK, PHASE-I NATIONAL HIGHWAY NO. 8A ROAD, RAJODA BAVLA Gujarat - 382220</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
           <t>24AAFCI5058Q1Z2</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
           <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
         </is>
       </c>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
-      <c r="P94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Nanjundeswara control panels</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>099451 91615</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>13, Magadi Main Rd</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Lakshmi Control Systems- Electrical control panel manufacturers in Bangalore | Cable Tray manufacturers in Bangalore</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>099005 15815</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>560091</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Anu Controls - Industrial Electrical Control Panels in Bangalore</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>098867 82549</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>No. 21, 10th Cross</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>SLD CONTROL SYSTEMS</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>097414 28001</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>46, Sir M.Visvesvaraya industrial layout</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>REGENCY ELECTRICALS PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>080 4120 3616</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>B No, 125, 2nd Main Rd</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Robin Electro Controls</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>078298 12133</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>49/8, 2nd B Cross Rd</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Chethan Power Enterprises</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>099455 13558</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>SY. No.18, #39, THOTADA RAJAMMA’S GARDEN, KANAKAPURA ROAD, JARAGANAHALLI, J.P.NAGAR POST</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>R.V CONTROLS</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>098450 98603</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Gundamma Compound, Rajiv Gandhi Road, G.K.M, Rod</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Panel board manufacturing</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>081053 27780</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>unverified: industry not supplied; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Bhuvanesh Power Control Panel board manufacturer</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>WG2V+MR8, Gubbalaala Main Rd</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Wovolt Electricals and Distributers #1 Wholesale Electrical Shop</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>096638 79374</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2nd floor, Vijayalakshmi Theatre, Old Taluk Cutchery Rd</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Amar Electrical Enterprises</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>080 4114 3350</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Ganga Complex, 25, AM Ln, near Vijay Vihar Hotel</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Shiyal Electric CO</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>085499 99979</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>No 1/2, Shiyal Towers, 3rd Cross Rd</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Chayaputhra Services</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>099454 52953</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>256/42. S G Kaval , Metro quarters road, Pipeline Rd</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Aimtech Electrical Control Panel</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>099000 15660</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>No. 569, Sri Kirana, 13th Cross, Bhavani Nagar, 15th Main Rd</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>SG ELECTRICALS</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>099010 01829</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>GANGA COMPLEX, 3, AM Ln</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Kushal Electricals</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>063616 89226</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>52,1st floor,2nd cross, M.t street, BVK Iyengar Rd</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>VIJAY ELECTRIC CORPORATION</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>098863 77214</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>SHETTY KRISHNAPPA LANE, NO 7 1ST CROSS ROAD, BVK Iyengar Rd, near HOTEL SHALIMAR, behind raj lights</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>STHAVISTAH AUTOMATION PVT LTD</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>096064 43946</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Seegehalli Rd, beside Govt ITI college</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Popular Electronics</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>090081 54599</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>26 th ,cross, Bagalagunte Main Rd</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>RIDDHI SIDDHI ELECTRICALS</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>090086 09953</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>13, M.T Street, BVK Iyengar Rd</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Power Control Equipments</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>37, Gowdanpalya Main Rd</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Elcab Engineers</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>094490 59000</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Sy.No.1193, VR Cinema Theater Complex, 34/4, Kengeri Ring Rd, behind HP Petrol Pump</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>VIJAYA BHASKAR SWITCH BOARD</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>098454 42302</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>56 magadi road, 5th Cross</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Sri Guru Electrical</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>099649 45010</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>73 &amp; 29/1, Armugam Mudaliayar Lane</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Tirupati Traders</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>095343 81522</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>tirupatitradersjpn@gmail.com</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Vijaya Plaza, Kothnur Main Rd, BK Circle JP Nagar 8th Phase, Bangalore 560076 Ph.: 9534381522</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>19ALAPM8429J1ZP</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>1 Lakh</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>S N S electro controls and switchgear</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>XFXV+C58</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Bhavani Electricals &amp; Lighting</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>096065 13449</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Shop No. 1 K.V. Shankara Building 7th Cross, Doddamara Rd</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>50 Lakh</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Pai Power Solutions</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>090089 02222</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>paipowersolutions@gmail.com</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Ambika Conner, West Side Service Road, 3M-219, Outer Ring Rd</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>29ABKPM0992J1Z3</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Rs. 40 lakhs to 1.5 Cr.</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Maa Ambe electricals &amp; electronics, Ups inverter battery</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>098457 63832</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>ground floor, 4, Sarjapur Main Rd, opp. Kotak mahindra bank</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Cauvery Powers</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Nine Switches</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>094296 92550</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>cauverypowers@gmail.com</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>#70, A M Lane, Chickpet, Bengaluru, Karnataka - 560053</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>29AAUFC9591Q1ZZ</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>1 Lakh</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>THANVI POWER SOLUTIONS WHOLESALE DEALER LUMINOUS &amp;EXIDE UPS &amp; BATTERY</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>097389 75197</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Ground Floor, Muni Reddy Building, Munnekollal Main Road Marathalli Opp Andhra Bank, Munnekollal</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Shri mataji electrical and electronics</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>099281 41387</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Gottigere post, Premises bearing Shop Ned In No.37, Central Excise Co Operative Society Layout, Noble Residency Road, Doddakammanahalli Road, Bannerghatta Rd</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Lunkad Electric Stores</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>098442 27410</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>29, BVK Iyengar Rd</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>29ACMPK1906H1ZI</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>1 Lakh</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>SV Enterprises</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>090604 05480</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>sales@sventerprises.co.in</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>No 104 3rd Cross 4th Main BDA 12th Block Opposite BDA Park Nagarbhavi 2nd Stage Bangalore 560072.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>29GFKPA2536C1ZO</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>1 Lakh</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Harshitha Switch Gear</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>No:56, 1, Magadi Main Rd</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>29CAEPP1034P1ZB</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Rs. 1.5 Cr. to 5 Cr.</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Meenakshi Plus (Panasonic Lighting and Anchor Fans Distributor)</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>no.12, 1, 2nd Cross Rd</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>SRI NITYA POWER SOLUTIONS ( LUMINOUS EXIDE AMARON INVERTER BATTERY SHOP ) SALES &amp; SERVICES</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>098441 23366</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>srinityapowersolutions@gmail.com</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>8/2, FCI Main Road Near Maremma Temple Channsandra, circle, Kadugodi, Bengaluru, Karnataka 560067</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>SHREYANS ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>082174 06792</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>support@asiameter.com</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>No.2, 9th Avenue Business Park, Ground Floor 002, Opposite Indian Bank, Near Makkala Koota Garden, Chamarajpet 5th Main Road, Bangalore – 560018</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>29AEUFS3579J1ZX</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>1 Lakh</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>NANDINI ELECTRICALS</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>098809 34504</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>nandinielectricalsystems@gmail.com</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Bengaluru, Karnataka, 560100</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>29ACDPN2362F1ZO</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>1 Lakh</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>adityaautocomponents</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>094483 74377</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>info@adityaac.com</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>#413, 9th Cross, Pete Chennappa Indl. Estate, Kamakshipalya, Bangalore IN 560079</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr"/>
+      <c r="P135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>GLOBAL AUTO COMPONENTS // MOLEX, JST/TE, TYCO, AMP, HRS, SUMITOMO, YAZAKI , KET , SAMTEC, 3M</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr"/>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>095139 69966</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>sales@globalautocomponents.co.in</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>No.3830, Ground Floor, Girinagar 4th Phase additional,2nd A Cross Cauvery Road, Banashankari 3rd Stage, (Near Cake of the Day) Bengaluru – 560085</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
+      <c r="O136" t="inlineStr"/>
+      <c r="P136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Hamson Automotive</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr"/>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>+918078102515</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>dialndial.marketing@gmail.com</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>NO 10, 3rd Cross Rd, Health Layout, Sunkadakatte, Bengaluru, Karnataka</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
+      <c r="O137" t="inlineStr"/>
+      <c r="P137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Bangalore Auto Parts</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr"/>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>+91 8618713187</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>bangaloreautoparts1@gmail.com</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>No 44 Old No 149 3rd Cross 1st Floor Bysandra Main Road, Jayanagar 1st Block, Bangalore, 560011</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>33AAMFB9768Q1ZG</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>1 Lakh</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>unverified: employee count unavailable</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr"/>
+      <c r="P138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Maruthi Auto Components</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr"/>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>082961 13423</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>2G67+F6P, 8th Cross Rd</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>29AFWPG9138A1Z4</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>1 Lakh</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
+      <c r="O139" t="inlineStr"/>
+      <c r="P139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>dC Auto Parts Pvt. Limited</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Pune - Bengaluru Hwy</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
+      <c r="O140" t="inlineStr"/>
+      <c r="P140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Toyota Industries Engine India Private Limited</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Mr. Keiichi Ido</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>tiei@tiei.toyota-industries.com</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Plot No 9, Phase II Jigani Industrial Area, Jigani, Bangalore 560105</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>29AAACK7425Q1ZW</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>26.7 Billion</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>unverified: employee count unavailable</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr"/>
+      <c r="P141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>GLOBAL AUTO PARTS</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>119/9, Lalbagh Fort Rd</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>29AAHFG8400D1ZL</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>2502080 Million</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>unverified: employee count unavailable</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
+      <c r="O142" t="inlineStr"/>
+      <c r="P142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Gi Auto Private Limited</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>080 2525 2437</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>jagadeesh@giauto.co.in</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>628/A, II FLOOR, ABOVE CANARA BANK, 1 ST STAGE INDIRANAGAR, BANGALORE - 560 038. INDIA</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
+      <c r="O143" t="inlineStr"/>
+      <c r="P143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Top Level Car Accessories</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr"/>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>089518 43398</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Tq, near Nandishwara theater Tent</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
+      <c r="O144" t="inlineStr"/>
+      <c r="P144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Tata Yazaki Auto Comp Limited</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr"/>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>319(p, Bommasandra Jigani Link Rd</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
+      <c r="O145" t="inlineStr"/>
+      <c r="P145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Avinash Automobiles</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr"/>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>099458 88887</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>avinashjadhav293@gmail.com</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>H. NO. 944, OTUR ROAD TALUKA KALWAN, DIST. NASHIK KALWAN Nashik Maharashtra - 425001</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
+      <c r="O146" t="inlineStr"/>
+      <c r="P146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Nexteer Automotive</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>nexteer.contact@nexteer.com</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>2nd Floor, Block 2B, Hibiscus, Embassy Tech Village,, Marathahalli Ring Road, Devarabeesanahalli, Bangalore – 560103,</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
+      <c r="O147" t="inlineStr"/>
+      <c r="P147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>jigani</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr"/>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>papannajigani@gmail.com</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>C/O KAMYA RAJENDRAN, 15 K, 169 ALAHALLI (V), UTTARAH, Konanakunte, Bangalore, Bangalore, Karnataka, India, 560062 - 560062</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
+      <c r="O148" t="inlineStr"/>
+      <c r="P148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Fine Components and Tools Pvt Ltd Unit 1 Gate No.02</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr"/>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>31, Bommasandra Jigani Link Rd</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
+      <c r="O149" t="inlineStr"/>
+      <c r="P149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Viana AutoZone</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr"/>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>086183 90776</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Jigani 2A, Plot 47</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
+      <c r="O150" t="inlineStr"/>
+      <c r="P150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Lamda Components Pvt Ltd.</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Lamda Components</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>076193 11331</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>sales@lamdacomponents.com</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Plot No.30, Veerasandra Industrial Area, Bangalore – 560 100, Karnataka, India.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
+      <c r="O151" t="inlineStr"/>
+      <c r="P151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Sansera Engineering</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr"/>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>080 2783 9309</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>madhukar_bhat@sansera.in</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>#26/6,Yarandahalli,Jigani Hobli,Anekal Taluk, Bommasandra Industrial Area,Bangalore-560099</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
+      <c r="O152" t="inlineStr"/>
+      <c r="P152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Sri Varalakshmi Auto Components Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr"/>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>099720 36978</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>4th &amp;, No. 2 &amp; 3, 5th Cross, near Sunkadakatte</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
+      <c r="O153" t="inlineStr"/>
+      <c r="P153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>AMJ Auto Components</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>098455 24875</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>65/38, Rangappa Layout, 2nd cross, Post</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
+      <c r="O154" t="inlineStr"/>
+      <c r="P154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Ace Forge Private Limited</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr"/>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>063639 22746</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>+916363922746</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>No.64, 2nd Phase, Jigani Industrial Area, Anekal Taluk, Bangalore- 562106</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
+      <c r="O155" t="inlineStr"/>
+      <c r="P155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Modtech Engineering</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr"/>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>098458 85811</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Bommasandra Jigani Link Rd, behind Omax auto 95</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
+      <c r="O156" t="inlineStr"/>
+      <c r="P156" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P94"/>
+  <autoFilter ref="A1:P156"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
 </worksheet>

--- a/backend/exports/All_Extracted_Leads.xlsx
+++ b/backend/exports/All_Extracted_Leads.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="__lead_export_mapping__" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'LeadCommonImportDTO'!$A$1:$P$156</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'LeadCommonImportDTO'!$A$1:$P$177</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -930,7 +930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P156"/>
+  <dimension ref="A1:P177"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.88671875" defaultRowHeight="12" customHeight="1"/>
   <cols>
     <col width="11.109375" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
@@ -5091,9 +5091,6 @@
           <t>adityaautocomponents</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr"/>
-      <c r="D135" t="inlineStr"/>
-      <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
           <t>094483 74377</t>
@@ -5114,17 +5111,11 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
       </c>
-      <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
-      <c r="O135" t="inlineStr"/>
-      <c r="P135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5137,9 +5128,6 @@
           <t>GLOBAL AUTO COMPONENTS // MOLEX, JST/TE, TYCO, AMP, HRS, SUMITOMO, YAZAKI , KET , SAMTEC, 3M</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr"/>
-      <c r="D136" t="inlineStr"/>
-      <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
           <t>095139 69966</t>
@@ -5160,17 +5148,11 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr">
         <is>
           <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
       </c>
-      <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
-      <c r="O136" t="inlineStr"/>
-      <c r="P136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5183,9 +5165,6 @@
           <t>Hamson Automotive</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr"/>
-      <c r="D137" t="inlineStr"/>
-      <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
           <t>+918078102515</t>
@@ -5206,17 +5185,11 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
       </c>
-      <c r="M137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
-      <c r="O137" t="inlineStr"/>
-      <c r="P137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5229,9 +5202,6 @@
           <t>Bangalore Auto Parts</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr"/>
-      <c r="D138" t="inlineStr"/>
-      <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
           <t>+91 8618713187</t>
@@ -5267,10 +5237,6 @@
           <t>unverified: employee count unavailable</t>
         </is>
       </c>
-      <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
-      <c r="O138" t="inlineStr"/>
-      <c r="P138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5283,21 +5249,16 @@
           <t>Maruthi Auto Components</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr"/>
-      <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
           <t>082961 13423</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr">
         <is>
           <t>2G67+F6P, 8th Cross Rd</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr">
         <is>
           <t>29AFWPG9138A1Z4</t>
@@ -5313,10 +5274,6 @@
           <t>unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
         </is>
       </c>
-      <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
-      <c r="O139" t="inlineStr"/>
-      <c r="P139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5329,11 +5286,6 @@
           <t>dC Auto Parts Pvt. Limited</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr"/>
-      <c r="D140" t="inlineStr"/>
-      <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr">
         <is>
           <t>Pune - Bengaluru Hwy</t>
@@ -5344,17 +5296,11 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr">
         <is>
           <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
       </c>
-      <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
-      <c r="O140" t="inlineStr"/>
-      <c r="P140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5367,7 +5313,6 @@
           <t>Toyota Industries Engine India Private Limited</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
           <t>Mr. Keiichi Ido</t>
@@ -5378,7 +5323,6 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
           <t>tiei@tiei.toyota-industries.com</t>
@@ -5409,10 +5353,6 @@
           <t>unverified: employee count unavailable</t>
         </is>
       </c>
-      <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
-      <c r="O141" t="inlineStr"/>
-      <c r="P141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5425,11 +5365,6 @@
           <t>GLOBAL AUTO PARTS</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr"/>
-      <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr">
         <is>
           <t>119/9, Lalbagh Fort Rd</t>
@@ -5455,10 +5390,6 @@
           <t>unverified: employee count unavailable</t>
         </is>
       </c>
-      <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
-      <c r="O142" t="inlineStr"/>
-      <c r="P142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5471,9 +5402,6 @@
           <t>Gi Auto Private Limited</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr"/>
-      <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
           <t>080 2525 2437</t>
@@ -5494,17 +5422,11 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
       </c>
-      <c r="M143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
-      <c r="O143" t="inlineStr"/>
-      <c r="P143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5517,32 +5439,21 @@
           <t>Top Level Car Accessories</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr"/>
-      <c r="D144" t="inlineStr"/>
-      <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
           <t>089518 43398</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr">
         <is>
           <t>Tq, near Nandishwara theater Tent</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
         </is>
       </c>
-      <c r="M144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
-      <c r="O144" t="inlineStr"/>
-      <c r="P144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5555,28 +5466,16 @@
           <t>Tata Yazaki Auto Comp Limited</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr"/>
-      <c r="D145" t="inlineStr"/>
-      <c r="E145" t="inlineStr"/>
-      <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr">
         <is>
           <t>319(p, Bommasandra Jigani Link Rd</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr">
         <is>
           <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
         </is>
       </c>
-      <c r="M145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
-      <c r="O145" t="inlineStr"/>
-      <c r="P145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5589,9 +5488,6 @@
           <t>Avinash Automobiles</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr"/>
-      <c r="D146" t="inlineStr"/>
-      <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
           <t>099458 88887</t>
@@ -5607,18 +5503,11 @@
           <t>H. NO. 944, OTUR ROAD TALUKA KALWAN, DIST. NASHIK KALWAN Nashik Maharashtra - 425001</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
         </is>
       </c>
-      <c r="M146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
-      <c r="O146" t="inlineStr"/>
-      <c r="P146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5631,10 +5520,6 @@
           <t>Nexteer Automotive</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr"/>
-      <c r="D147" t="inlineStr"/>
-      <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr">
         <is>
           <t>nexteer.contact@nexteer.com</t>
@@ -5650,17 +5535,11 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="J147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr">
         <is>
           <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
       </c>
-      <c r="M147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
-      <c r="O147" t="inlineStr"/>
-      <c r="P147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5673,10 +5552,6 @@
           <t>jigani</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr"/>
-      <c r="D148" t="inlineStr"/>
-      <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr">
         <is>
           <t>papannajigani@gmail.com</t>
@@ -5692,17 +5567,11 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
       </c>
-      <c r="M148" t="inlineStr"/>
-      <c r="N148" t="inlineStr"/>
-      <c r="O148" t="inlineStr"/>
-      <c r="P148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5715,28 +5584,16 @@
           <t>Fine Components and Tools Pvt Ltd Unit 1 Gate No.02</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr"/>
-      <c r="D149" t="inlineStr"/>
-      <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr">
         <is>
           <t>31, Bommasandra Jigani Link Rd</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
         </is>
       </c>
-      <c r="M149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
-      <c r="O149" t="inlineStr"/>
-      <c r="P149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5749,15 +5606,11 @@
           <t>Viana AutoZone</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr"/>
-      <c r="D150" t="inlineStr"/>
-      <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
           <t>086183 90776</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr">
         <is>
           <t>Jigani 2A, Plot 47</t>
@@ -5768,17 +5621,11 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="J150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr">
         <is>
           <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
       </c>
-      <c r="M150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
-      <c r="O150" t="inlineStr"/>
-      <c r="P150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5791,7 +5638,6 @@
           <t>Lamda Components Pvt Ltd.</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
           <t>Lamda Components</t>
@@ -5822,17 +5668,11 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr">
         <is>
           <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
       </c>
-      <c r="M151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
-      <c r="O151" t="inlineStr"/>
-      <c r="P151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5845,9 +5685,6 @@
           <t>Sansera Engineering</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr"/>
-      <c r="D152" t="inlineStr"/>
-      <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
           <t>080 2783 9309</t>
@@ -5868,17 +5705,11 @@
           <t>Bangalore</t>
         </is>
       </c>
-      <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
       </c>
-      <c r="M152" t="inlineStr"/>
-      <c r="N152" t="inlineStr"/>
-      <c r="O152" t="inlineStr"/>
-      <c r="P152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5891,32 +5722,21 @@
           <t>Sri Varalakshmi Auto Components Pvt. Ltd.</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr"/>
-      <c r="D153" t="inlineStr"/>
-      <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
           <t>099720 36978</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr">
         <is>
           <t>4th &amp;, No. 2 &amp; 3, 5th Cross, near Sunkadakatte</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr">
         <is>
           <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
         </is>
       </c>
-      <c r="M153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
-      <c r="O153" t="inlineStr"/>
-      <c r="P153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5929,15 +5749,11 @@
           <t>AMJ Auto Components</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr"/>
-      <c r="D154" t="inlineStr"/>
-      <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
           <t>098455 24875</t>
         </is>
       </c>
-      <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr">
         <is>
           <t>65/38, Rangappa Layout, 2nd cross, Post</t>
@@ -5948,17 +5764,11 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr">
         <is>
           <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
       </c>
-      <c r="M154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
-      <c r="O154" t="inlineStr"/>
-      <c r="P154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5971,9 +5781,6 @@
           <t>Ace Forge Private Limited</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr"/>
-      <c r="D155" t="inlineStr"/>
-      <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
           <t>063639 22746</t>
@@ -5994,17 +5801,11 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="J155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr">
         <is>
           <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
       </c>
-      <c r="M155" t="inlineStr"/>
-      <c r="N155" t="inlineStr"/>
-      <c r="O155" t="inlineStr"/>
-      <c r="P155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6017,35 +5818,696 @@
           <t>Modtech Engineering</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr"/>
-      <c r="D156" t="inlineStr"/>
-      <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
           <t>098458 85811</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr">
         <is>
           <t>Bommasandra Jigani Link Rd, behind Omax auto 95</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr">
         <is>
           <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
         </is>
       </c>
-      <c r="M156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
-      <c r="O156" t="inlineStr"/>
-      <c r="P156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Jaggi Industries</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Mr Sukhvinder Singh</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>080 4547 8560</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>B-62, Mayapuri Industrial Area, Phase-II,New Delhi - 110064, India</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>07AAEFJ9793R1Z8</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Rs. 5 Cr. to 25 Cr.</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Neerflow Pumps LLP</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>099110 04200</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>info@neerflow.com</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>C-83, Mayapuri Industrial Area, Phase-II 110064, New Delhi</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Indraprastha Gas Limited CNG Station</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>074289 44273</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Plot No. 4, Community Centre,, Sector 9, R K Puram, New Delhi - 110022</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>NARAYAN WATER PUMP &amp; Pressure Pump - Plumbers &amp; Electrician</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>092785 44293</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Sector-1, Pocket-00, book Depot Road, nearby Kanjhawala Road</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>TULFI Point-Sector 8 Petrol Pump</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>P43C+2P8</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>igl cng pump</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>P3HX+362</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Bharat Petroleum, Petrol Pump -Sanjeev Filling Station</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>unverified: industry not supplied; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Fluid Frontliners</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Anurag Kalra</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>080 4389 1650</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>58, G.B Road, Shardhanad Marg, New Delhi - 110006, Delhi, India</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>07APQPK5379F1ZE</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>25 Cr</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>The Pump Factory</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>099908 05408</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Lakhiramchowk, opposite The Great Ashoka public school</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Police Petrol Pump Pitampura</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>1, Police Lines, near Marble Market</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Indane Petrol pump and cng station</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>P466+J2C</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Bharat Petroleum, Petrol Pump -Shaurya Bhushan Filling Station</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>RAM KRISHAN MARG DELHI</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Archana Trading Company (ATC)</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Micromulti Grease</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>098186 17872</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>info@archanatradingcompany.com</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Third Floor, back side, C-75</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Rattan Hose &amp; Engineering Works Pvt. Limited.</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>011 4709 6666</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>info@rattanhose.com</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>C-67, Mayapuri Industrial Area, Phase-II, New Delhi-110064, (India)</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>GRECO CNG</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>098197 49380</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>A-14</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Ace Automation Engineers</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>011 4554 6564</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>oilcoolers@acefluidpower.com</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Compared to water cooling systems, air cooled oil coolers are easy to install, require less maintenance and are more cost effective. They are widely used in CNC machines, hydraulic power packs, gear boxes, presses, injection moulding machines and many other heavy duty applications. A good quality oil cooler helps in increasing machine life, reducing breakdown time and improving overall productivity., C-164, Mayapuri Industrial Area,, Phase II, New Delhi – 110064, India</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Hydmark Applicon</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>011 4511 4611</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>sales@hydmark.com</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>A- 5/4 &amp; 6/4, Phase- 2,, Mayapuri Industrial Area, New Delhi - 110064, India</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>IMMENSE VALVE INDIA PVT LTD</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>099672 45659</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>UNIT 805, CRESCENT BUSINESS SQUARE, opp. SJ STUDIO METRO, near SAKINAKA</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Maham Valves Automation</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>077388 53658</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>unverified: industry not supplied; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>GLOBAL STEEL &amp; ENGINEERING</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>099301 95335</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>163, Dr. MG Mahimtura Marg</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>JHON VALVES EXIM INDIA (SS DAIRY FITTINGS AND SS DAIRY VALVES IN MUMBAI,PIPE FILTER,AMUL DRAIN TRAP,SS MANHOLE COVER)</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>093228 78406</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>sales@jhonvalves.com</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Regd.Office No 10 2nd Floor, Aman House</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P156"/>
+  <autoFilter ref="A1:P177"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
 </worksheet>

--- a/backend/exports/All_Extracted_Leads.xlsx
+++ b/backend/exports/All_Extracted_Leads.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="__lead_export_mapping__" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'LeadCommonImportDTO'!$A$1:$P$177</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'LeadCommonImportDTO'!$A$1:$P$329</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -930,7 +930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P177"/>
+  <dimension ref="A1:P329"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.88671875" defaultRowHeight="12" customHeight="1"/>
   <cols>
     <col width="11.109375" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
@@ -943,7 +943,7 @@
     <col width="50" customWidth="1" style="2" min="8" max="8"/>
     <col width="29.21875" customWidth="1" style="2" min="9" max="9"/>
     <col width="20.5546875" customWidth="1" style="2" min="10" max="10"/>
-    <col width="25" customWidth="1" style="2" min="11" max="11"/>
+    <col width="28" customWidth="1" style="2" min="11" max="11"/>
     <col width="50" customWidth="1" style="2" min="12" max="12"/>
     <col width="15.5546875" customWidth="1" style="2" min="13" max="13"/>
     <col width="21.109375" customWidth="1" style="2" min="14" max="14"/>
@@ -6506,8 +6506,4797 @@
         </is>
       </c>
     </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>KVS Automatic Water Level Controller (Fully Automatic System)</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>080727 01588</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>No.1/1, S/S Complex, Thanjavur Rd</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>EASWARAN ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Ibrahim park back side, 1E, Jalal Kudiri Street, W Blvd Rd</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Vaidheswaran industries</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>094426 42839</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>SIDCO INDUSTRIAL ESTATE, B8</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>HVK Systems &amp; Marketing Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>0422 230 0039</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>1485, Trichy Rd, Behind Elgin Ultra</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Tiruchirappalli</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>KAMAK</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>091500 47571</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Passport office, Kamak Associates 148, Old, W Blvd Rd, opp. New SBI Siruthozlil Branch</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>HTC Pipes &amp; fittings</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>097909 45934</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Plot 91</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>SRI Energy, Inc.</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>25521905</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>SF.NO. 115/4A, Vadugapatti Village, Illupur Taluk, Pudukottai District</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Power Trans Engineering</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>86, 87</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>ELLEM Engineering</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>098431 52005</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Sf no 99/2A, 13C,Sree Maruthi industrial Estate,</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Christor Taps &amp; Fittings</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>094431 58717</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>lks tower, 127/2, W Blvd Rd</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Tiruchchirappalli</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>London Hardwares Shop Trichy</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>098656 01786</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Devar Hall, Water Tank Shopping Complex, GF 8, W Blvd Rd</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Tiruchchirappalli</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Salem Auto Parts</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>unverified: industry not supplied; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>SALEM AUTO SOLUTIONS</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>088258 22655</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>No.132, Suramangalam Main Rd</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Vikas Cars Accessories (All Car Accessories Dealer in Salem)</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>099947 99115</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>250/10, Meyyanur Main Rd</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Jagadamba Auto Agencies</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>J5X5+GM4</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>KM CAR DECORS</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>M4FM+H59, Meyyanur Main Rd</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>SEM ENTERPRISES PVT LTD</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>0427 233 5277</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>SRI P. R AARCADE,, 230, Itteri Rd</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Rollz Cars (Car A/C Spars &amp; Services &amp; Pre Owned Cars Buying/Selling)</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>096295 23223</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>226A, Omalur Main Rd</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Siyon auto consulting</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>095668 10888</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>MDR439</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Jeyam Cool Spares</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>073737 67626</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>145/3, VMR Nagar Rd, near ARRS theatre</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Mahalakshmi Auto Centre</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>0427 426 5486</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>64/4 New East Pullikuthi Street</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>JEM Indiaa</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>090922 06362</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Thandavarayan oil Mill Compound, 406-1, Suramangalam Main Rd</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Racing Car Point</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>097912 71150</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>J4MF+QR7</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Mytvs Car Accessories - Car Parlour</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>#222, silver Arrow Complex, 4 Roads Piller No. S72, opp. Church</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>MSB ELECTRONIC INDUSTRIES</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>098427 55449</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>51/12 chennan krisha puram</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Hutaib Engineering Company</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>099445 72993</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>95 D.D ROAD, Old Bus Stand Rd, opp. SANGAM COMPLEX, near ALANKAR THEATRE</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Muthuraj Automobiles</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>0424 226 9309</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>35(25, Agilmedu 7th Streer</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Sree Meenakshi Auto Spares</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>099946 66885</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>18A/1 sathy Road, Municipal Colony Main Rd</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Sree Meenakshi Automobiles</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>094871 06885</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>82, Perundurai Rd, opp. to kvb bank</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Erode</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>XTREMZ Bike Accessories</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>098425 83338</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Sathiya Street, 275/1, Municipal Colony Main Rd</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Amman Auto Parts</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>094433 58802</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>1st cross, Jai balaji Nagar, Naal Rd</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Tamilnadu Auto Stores</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>099655 22578</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>21/2, P.A. Complex Behind Parimalam Complex, Road, Periyanna St</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Vijay Car Care &amp; Decors in Erode | Car Accessories Shop in Erode | Car Wash in Erode | Multi Brand Car Accessories in Erode</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>098421 32068</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>147/2, Nasiyanur Rd</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Erode</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Sri Giri Auto Stores</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>098423 92924</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>389/1, Visakan Tower, Perundurai Rd</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Erode</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>A-Team Auto Spares</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>098423 26325</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>370/2A, Perundurai Rd, near Ambal Auto</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Erode</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Sri Senthil Autos - Hero MotoCorp</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>092899 22135</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>134 B, Perundurai Rd</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Erode</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>SHRI VIGNESH CAR JEWELS</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>098428 65000</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>135, Perundurai Rd, opp. Ambal auto</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Erode</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>AAUDIO ONE ERODE</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>098423 73379</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>106/2, Perundurai Rd</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Erode</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>THIYAGU AUTOMOTIVES ERODE</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>075027 53172</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>unverified: industry not supplied; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>The Noble Motor (Noble Servece)</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Perundurai Rd, near TPN hospital</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Erode</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>River Service Perundurai Road</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>092402 21746</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Building No: 314 / 2A2, Chinna Sengodampalayam, Perundurai Rd</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Erode</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Vinayaka Tyress</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>099949 29494</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>236, Chinnamuthu Main St</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Erode</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Montra Electric - Adharvaa Electric Autos, Erode</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>08071 639 009</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>No 1/568, Perundurai Road, Vallipurathanpalayam, beside Tractor Service Centre</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Erode</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Ashok Leyland Dost Erode</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>063803 23280</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>13/2, Perundurai Rd</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Erode</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>River Store Perundurai Road</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>092402 56420</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Chinna Kaadu Thottam, No: 314/2A2, Perundurai Rd, near Veerappampalayam Bypass</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Erode</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Kia Car Showroom - Pressana Kia Chinna Sengodampalayam, Erode</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>063844 44500</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>72/83, Sengodampalayam Rd</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Iswarya Cars</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>098425 37575</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>6, OA Ramasamy St</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Harris Car Covers</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>097503 82222</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>207, Perundurai Rd, near Sri Vari Arangam</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Erode</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Oragadam</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>swathilands@gmail.com</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>unverified: industry not supplied; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Transindia Control Systems Pvt.Ltd.</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>040 2781 0199</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>tic@transindiacontrols.in</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Anjuman Campus,, 1st Floor, Beside Anjuman Office,, 125. M.G.Road, Secunderabad - 500003</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Secunderabad</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>ALL-TEC ELECTRICAL ENGINEERS</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>098663 19925</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>201,5-2-437, Seven Hills Villa, Rashtrapati Rd, opp. Arya Samaj Building Office</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Jothi Batteries</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>099443 42723</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>4B, Sankara Naidu St</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Cuddalore Old Town</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Janakiram&amp;Co (2 Wheeler spares)</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>PQX6+R9H</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Swaraj Tractors - M/S Sree Sakthi Automobiles</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>08071 433 657</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Shop No 3, Varsha Garden Imperial Road, Two Way Road, nearby Virudhachalam - Cuddalore Road</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Force Motors - Thangam Force</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>063840 01421</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>VSP Krishnamurthy Reddiyar Nagar, 5, Nellikuppam Main Rd</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Kubota Tractor - Pondy Agricultural Machinery</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Shop No 3, Nellikuppam Main Rd, nearby Indianoil Petrol Pump</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Cuddalore</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Royal Enfield Service Center - Rooster Automobiles</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>088795 17692</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Chellankuppam, 9, Imperial Rd</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Cuddalore</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Exide Care - Sri Devi Agencies</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>080 6955 8971</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>No 2, Saravana Complex, Mohan Singh St</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>KTM Husqvarna Cuddalore</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>093558 34384</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>unverified: industry not supplied; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Transture Solutions</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>080124 80157</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Sri Ram sewing machine</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>077083 90887</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>PQ8C+Q2V</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Kun Škoda Showroom</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>091769 49000</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>RS No 223/2B, Chidambaram Rd</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Murugan Electricals</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>094441 64334</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>10, S Park St</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Jai Mahaveer Electricals</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>098848 28022</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>No 126/10,Yadaval Street, Padi</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Electrical Control Panel</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>095511 72864</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>45GC+8HM, MM Ave 1st St</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Swaraj Motors</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>085470 54304</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>32ABPFM2499F1ZZ</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>18,217 Crore</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>unverified: industry not supplied; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Govind Auto Spares</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>095444 42009</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>Puliyarthala, Ulloor - Akkulam Rd</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>Thiruvananthapuram</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>MIDDLE EAST AUTO PARTS. PVT .LTD</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>085907 09144</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>Sasthamangalam Jct</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>Thiruvananthapuram</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Scrap vehicle buying</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>unverified: industry not supplied; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Candour Auto Tech Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>096332 22927</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>VP II, 1148, Nettayam Rd</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Amba Automobiles</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>089214 40702</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>Thakaraparambu Road TC 28/1923, 1-6</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Phoenix Car Spa</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>085939 99392</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>TC 13/ 352 (1) M.K Building Periyamkodu PO</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Old Bike scrap buyer</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>094007 35896</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>Pathiripally - Choozhampala Rd, near guru Mandram</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Xtremers - Auto hub</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>089218 74366</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>TC 6/1345, S-25, Anupama Nagar Pongummod</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Kabeer Used Bike Parts</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>T.c 38 2100, Melancode St</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Royal Enfield - Subha Auto Wares</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>0471 247 3020</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>Sitarama Building TC 80/2788 Attakulangara, Sreevaraham - Muckolakkal Rd</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>S.S SCRAPS &amp; METALS MART</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>079073 64753</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>unverified: industry not supplied; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>V M Auto Agencies</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>094475 35111</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>JX3X+M54 11th stone</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>Nedumangad</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>La Maison Citroën, Trivandrum</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>085939 77777</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>TC-91/1042-8, EVM Autokraft India Private Limited - Citroen, N H Byepass Venpalavattom, Kadakampally Rd</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Michelin Tyres - Travencore Wheel Club</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>097119 99124</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>TC 16/390, Indeevaram, Cotton Hill Rd</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Moto Avenue</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>083300 16943</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>LMS Junction, Union Tower</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>Thiruvananthapuram</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Mahindra Cherukara Vehicles - SUV &amp; Commercial Vehicle Showroom</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>088799 31870</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>Thiruvananthapuram N H Bypass Road, near IOCL petrol pump, Thrimoorthy Nagar, Muttathara Thiruvana</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>HITEC VALVES</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>094448 62329</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>hitecvalves@vsnl.net</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>No.3, Part I TASS Industrial Estate, Ambattur, Chennai – 600098, India</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>HP VALVES &amp; FITTINGS INDIA PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>S. Harichandran</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>044 2625 2537</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>sales@hpvalvesindia.com</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>SP-133, SIDCO Industrial Estate, Ambattur, Chennai - 600058, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Floport Valves Private Limited</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Mr. G. Hem Kumar</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>094440 55503</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>floportvalves@gmail.com</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>SP.29,AMBATTUR INDUSTRIALESTATE,AMBATTUR MADRAS-58 TAMILNADU, TAMILNADU, Tamil Nadu, India, 600058 - 600058</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>ValvTechnologies</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>7138600400</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>info@valv.com</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>PLOT NO. 65,FUNCTIONAL DEVELOPMENT, PLOTS FOR ELECTRICAL ELECTRONICS INDUSTRIES OMR, P, ERUNGUDI, Chennai, CHENNAI, Tamil Nadu, India, 600096 - 600096</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Sakthi Industries-Excel Valves</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>099629 95721</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>sakthivalves@gmail.com</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>Plot No.1, 10th Street, Kamarajar Road, TASS Industrial Estate, Ambattur, Chennai 600 098, INDIA</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>www.hussainenterprise.in</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>091502 97330</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>navkarinte@yahoo.co.in</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>188 (New No. 268), Linghi Chetty Street, Chennai - 600 001</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>FLUID VALVE CO KELLYS GODOWN</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>36PW+MG2</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>S. J. Industries</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>098403 50439</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>sales@analapumps.com</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>73, Tass Industrial Estate, Ambattur, Chennai - 600 098. Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Bharat Petroleum - Nironka Royal Agency</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>45C9+2G8</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Autocom Industries</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>4555+J8X.320</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>VBM ENGINEERING PRODUCTS</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>unverified: industry not supplied; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Lachu Auto Traders</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>098406 40582</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>No.17,18,19 Lajapathy raj street,opp to town bus stand gandhipuram cbe-641012, near Town Busstand</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Thanukkodi Aditya Auto Stores</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>0422 423 2777</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>No 408, 411, Dr Nanjappa Rd</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>Coimbatore</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>NEW RAJA TOOLS - AUTO GARAGE TOOLS COIMBATORE</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>098430 88854</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>NSP Complex, 180/ A/15, Dr Nanjappa Rd, opp. Royal Agencies Furniture</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>Coimbatore</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Sun Motor Parts</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>089251 02864</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>M.S.Nagar, Podanur Main Rd</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>Coimbatore</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Infinity Automobile Spares</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>082208 98350</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>unverified: industry not supplied; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>SS Car Accessories</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>099409 49074</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>0pp Nayara Petrol Bunk, 915, Dr Alagappa Chettiar Rd</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>Coimbatore</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Good Luck Motor Parts</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>093637 11882</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>5/164,Aringar Anna Nagar</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>South India Trading Agencies</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>098430 16110</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>Parsns Trade Plaza, 156, Dr Nanjappa Rd</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>Coimbatore</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>The Braap Shop</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>085080 55444</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>1233, Mettupalayam Main Rd, near Naga Sai Temple</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>GLOBAL MULTI TECH - Electric Vehicle Spares Wholesaler</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>063697 21254</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>1137-1138, Sukrawarpet St</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>AB pumps</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>099655 56165</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>9, 240C, Dr Nanjappa Rd</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>Coimbatore</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Vasanthi mill</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>4848+6HV</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>33AADFV2078E1ZD</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>25 Cr</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>V S Auto Electricals</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>099940 53011</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>1/801, Palavanjipalayam Ring Rd, near Sakthi hospital Kadeswara plywoods, opposite Dharapuram Main Road</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Tirupur Jobs</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>099760 93012</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>2/400 Rajendran compound</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Thiru annamalaiyar air compressor motor sales and servicee</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>090955 95465</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>new bus stand back side, 58/1A Lucky Nagar, Sathi theatre road</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>sivakasi auto parts</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>086088 12597</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>333/1, Virudhunagar Main Rd, opposite mukesh honda</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Saraswati Automobiles</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>088383 39521</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>Do. No. 792 Periya Karuppan Road Sivakasi Tamil Nadu 626123</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>Sivakasi</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>29EYVPP3328B1ZZ</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>SRI VALATHTHI AMMAN AUTOS</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>099941 21288</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>872/D Sivanadiyan Complex Kamak Road</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Star Auto Parts</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>094866 39903</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>500A, Virudhunagar Main Rd, opp. railway station</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>27ACGPH2998J1Z4</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover could not be parsed; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>MS Moto central helmet and accessories</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>FQ5X+RRX</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>SRI BAGAWATHI AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>098432 46699</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>6/3 Arun Sundari Complex</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Bismi car care</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>084385 02277</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>60AcharmanArnachalamRoad</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Sri raja auto spares</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>182/2, Vembakottai Rd</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>Sivakasi</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Auto Dynamics-Continental Tyres</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>079 4344 4312</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>231/2, Thiruthangal Rd, near SFR COLLEGE</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>M K GRAND AUTOMOBILES, SIVAKASI - BOSCH CAR SERVICE</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>091500 80077</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>S.NO-54/8A3A, THAYILPATTI VILLAGE MADATHUPATTI, MAIN RAOD, near IOCL PETROL PUMP</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Maruti Suzuki ARENA (Meenakshi Autozone, Sivakasi, Tiruthangal Road)</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>080 6221 6609</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>819, Thiruthangal Rd</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>Sivakasi</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>33AAKCM3378A1ZO</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>₹186.71 Crore</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Anbu Two Wheeler Spares</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>394/1A1 ALAMARATHUPATTI ROAD, Virudhunagar Main Rd</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Bikecenter accessories</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>096777 82020</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>unverified: industry not supplied; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>KAYYEM MOTORS</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>098421 54125</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>872B, Kamak Rd</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Haribala Auto Spares</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>FRJ7+X4V</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>mhadev auto mobiles</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>070142 33840</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>218, seethakathi middle street, near kamarajar park</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>33AZDPN2935P1Z0</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Rs. 0 to 40 lakhs</t>
+        </is>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>SPEED AUTO CARE &amp; PARTS</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>Sudharsan Garden, 1189/1A1A</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Devi Sri Motors</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>087781 33832</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>unverified: industry not supplied; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>HITEC VALVES</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>094448 62329</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>hitecvalves@vsnl.net</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>No.3, Part I TASS Industrial Estate, Ambattur, Chennai – 600098, India</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>HP VALVES &amp; FITTINGS INDIA PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>S. Harichandran</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>044 2625 2537</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>sales@hpvalvesindia.com</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>SP-133, SIDCO Industrial Estate, Ambattur, Chennai - 600058, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>33AACCH0510P1ZU</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>₹72.11 Crore</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Floport Valves Private Limited</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Mr. G. Hem Kumar</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>094440 55503</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>floportvalves@gmail.com</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>SP.29,AMBATTUR INDUSTRIALESTATE,AMBATTUR MADRAS-58 TAMILNADU, TAMILNADU, Tamil Nadu, India, 600058 - 600058</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>www.hussainenterprise.in</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>091502 97330</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>navkarinte@yahoo.co.in</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>188 (New No. 268), Linghi Chetty Street, Chennai - 600 001</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Sakthi Industries-Excel Valves</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>099629 95721</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>sakthivalves@gmail.com</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>Plot No.1, 10th Street, Kamarajar Road, TASS Industrial Estate, Ambattur, Chennai 600 098, INDIA</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>FLUID VALVE CO KELLYS GODOWN</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>36PW+MG2</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Humifogg Systems – Humidifier Manufacturer in Coimbatore</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>098422 57593</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>sales@humifoggsystems.com</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>Prevention of dryness, static discharge, and material degradation during storage, No:32, Indumaa Nagar, Vilankurichi Road, Near Cheranma Nagar, Coimbatore, Tamil Nadu 641035</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>Coimbatore</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>33AAEFH1275J1ZI</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>5 - 25 Cr</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>COSMIC PUMPS / ANNAM INDUSTRIES</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>099525 17732</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>Site No. 12, S.F No. 353/1, Cosmic Pumps Buildings,, Vinayagar Kovil Street, Neelikompalayam,, Coimbatore, Tamil Nadu 641033, India</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>Coimbatore</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Sarah pumps</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>098944 18218</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>302, Samraj trade centre, vilankuruchi main road, peelamedu</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>Coimbatore</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>AB pumps</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>099655 56165</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>9, 240C, Dr Nanjappa Rd</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>Coimbatore</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Santhi Agencies: Authorized CRI Pumps</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>099945 89339</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>33EKKPS4955N1ZA</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Rs. 40 lakhs to 1.5 Cr.</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>unverified: industry not supplied; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Hindustan Petroleum Corporation Limited</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>097875 33000</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>15644910@retail.hpcl.co.in</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>Coimbatore, Tamil Nadu - 641016</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>Coimbatore</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>₹4,414.48 Crore</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>MG MEDITECH</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr"/>
+      <c r="D316" t="inlineStr"/>
+      <c r="E316" t="inlineStr"/>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>078389 48874</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>mgmeditechindia@gmail.com</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>Head Office: Oﬃce No. SK A-27, Sector-112, Noida, Gautam Dudh Nagar (Uttar pradesh-201301)</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>Noida</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr"/>
+      <c r="K316" t="inlineStr"/>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr"/>
+      <c r="N316" t="inlineStr"/>
+      <c r="O316" t="inlineStr"/>
+      <c r="P316" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Medico Electrode</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr"/>
+      <c r="D317" t="inlineStr"/>
+      <c r="E317" t="inlineStr"/>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>0120 488 0600</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>Sales@MedicoElectrodes.com</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>Medico Electrodes International Limited,, Plot 142A / 11,12 &amp; 29, Noida Special Economic Zone, Noida – 201305</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>Noida</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>09AAHCM4229K1Z5</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>₹601.5 Crore</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: employee count unavailable</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr"/>
+      <c r="N317" t="inlineStr"/>
+      <c r="O317" t="inlineStr"/>
+      <c r="P317" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Vignaharta Enterprises Private Limited</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr"/>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Saket Agarwal</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>098769 78488</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>info@healthyjeenasikho.com</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>Whether you need a hospital bed, oxygen concentrator, CPAP/BiPAP machine, wheelchair, or patient monitor, we have it all!, 📍Noida Brand Store Google Location: Near Hanuman Murti, Sector-49, Noida, 201304</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>Noida</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>06AAECV9995Q1Z2</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>₹16.36 Crore</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: employee count unavailable</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr"/>
+      <c r="N318" t="inlineStr"/>
+      <c r="O318" t="inlineStr"/>
+      <c r="P318" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>iLife Medical Devices Pvt Ltd, Noida Office</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr"/>
+      <c r="D319" t="inlineStr"/>
+      <c r="E319" t="inlineStr"/>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>0120 320 0663</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>CARE@ILIFEMEDICA.COM</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>7, Sector 63 Rd</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>Noida</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>₹22.75 Crore</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: employee count unavailable</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr"/>
+      <c r="N319" t="inlineStr"/>
+      <c r="O319" t="inlineStr"/>
+      <c r="P319" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Divine Health Home Care</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr"/>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Moh Irshad</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>093551 00499</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>info@divinehealthathome.com</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>Gr. Noida West : 15A &amp; 22A, First Floor, Near Chunmun, Galaxy Blue Sapphire Plaza, Greater Noida West (Noida Extension), Uttar Pradesh 201301</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>Noida</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr"/>
+      <c r="K320" t="inlineStr"/>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+      <c r="M320" t="inlineStr"/>
+      <c r="N320" t="inlineStr"/>
+      <c r="O320" t="inlineStr"/>
+      <c r="P320" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Life Patient Home Care</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr"/>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Sameer Ahmed</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>084455 58377</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>lifepatienthomecare@gmail.com</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>P-38, MARKET, Block P, Sector 12, Noida, Uttar Pradesh 201301</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>Noida</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr"/>
+      <c r="K321" t="inlineStr"/>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr"/>
+      <c r="N321" t="inlineStr"/>
+      <c r="O321" t="inlineStr"/>
+      <c r="P321" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Coloplast India Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr"/>
+      <c r="D322" t="inlineStr"/>
+      <c r="E322" t="inlineStr"/>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>0120 407 1300</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr"/>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>IGL Complex, 4th Floor (Right Wing), Tower 3, Plot No. – 2B, Sector 126, Noida, Uttar Pradesh 201304</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>Noida</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>06AAECC3545K1ZN</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>₹134.33 Crore</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: employee count unavailable</t>
+        </is>
+      </c>
+      <c r="M322" t="inlineStr"/>
+      <c r="N322" t="inlineStr"/>
+      <c r="O322" t="inlineStr"/>
+      <c r="P322" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>JK Engineering Works</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr"/>
+      <c r="D323" t="inlineStr"/>
+      <c r="E323" t="inlineStr"/>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>082850 26446</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>info@jkenggindia.com</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>C-30, Sector-57, Noida – 201301, Uttar Pradesh, India</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>Noida</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr"/>
+      <c r="K323" t="inlineStr"/>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr"/>
+      <c r="N323" t="inlineStr"/>
+      <c r="O323" t="inlineStr"/>
+      <c r="P323" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Kuvera Organics Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr"/>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Mr Atul Kumar Gupta</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>098102 28335</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr"/>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>G-2514, Prateek Edifice, Sector 107,Noida - 201304, Uttar Pradesh, India</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>Noida</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>09AAJCK3965G1Z5</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>₹8 Crores</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: employee count unavailable</t>
+        </is>
+      </c>
+      <c r="M324" t="inlineStr"/>
+      <c r="N324" t="inlineStr"/>
+      <c r="O324" t="inlineStr"/>
+      <c r="P324" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Innovation Meditech Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr"/>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Rajeev Agarwal</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>098110 58389</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>info@innovationmeditech.com</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>📍 B-6, Sector-88, Noida, UP – 201304</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>Noida</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>09AADCI3200N1ZM</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>₹39.62 Crore</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: employee count unavailable</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr"/>
+      <c r="N325" t="inlineStr"/>
+      <c r="O325" t="inlineStr"/>
+      <c r="P325" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>SpeechGears</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr"/>
+      <c r="D326" t="inlineStr"/>
+      <c r="E326" t="inlineStr"/>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>097735 57256</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>marketing@speechgears.com</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>SpeechGears India, B-17, Sector 60, Noida, U.P., 201301</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>Noida</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>09AAICG9712G1ZD</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>₹4.99 Crore</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: employee count unavailable</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr"/>
+      <c r="N326" t="inlineStr"/>
+      <c r="O326" t="inlineStr"/>
+      <c r="P326" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>MB Plastic Industries</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr"/>
+      <c r="D327" t="inlineStr"/>
+      <c r="E327" t="inlineStr"/>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>+911204985442</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>sales@mbplastic.com</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>B-75, Sector 83, Noida, UP 201305 IN</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>Noida</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>09ADFPJ7518J1Z9</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Rs. 2.5 to 5 Crore Approx.</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: employee count unavailable</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr"/>
+      <c r="N327" t="inlineStr"/>
+      <c r="O327" t="inlineStr"/>
+      <c r="P327" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>OPTIAN HEALTHCARE PVT LTD</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr"/>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Reenu Gupta</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>011 6926 6203</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>info@optian.in</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>C25, Sector 8, Noida, Uttar Pradesh,201301</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>Noida</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>₹1.19 Cr</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>unverified: declared industry could not be matched to a target segment; unverified: employee count unavailable</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr"/>
+      <c r="N328" t="inlineStr"/>
+      <c r="O328" t="inlineStr"/>
+      <c r="P328" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>AB CONTRACTS</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr"/>
+      <c r="D329" t="inlineStr"/>
+      <c r="E329" t="inlineStr"/>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>011-46710423</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>helpdesk@tradeindia.com</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>148-B, Udyog Kendra-1, Ecotech-3, Greater Noida, Uttar Pradesh, 201303, India</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>Noida</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr"/>
+      <c r="K329" t="inlineStr"/>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr"/>
+      <c r="N329" t="inlineStr"/>
+      <c r="O329" t="inlineStr"/>
+      <c r="P329" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P177"/>
+  <autoFilter ref="A1:P329"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
 </worksheet>
